--- a/src/attributions/attributions_ig_traj_243.xlsx
+++ b/src/attributions/attributions_ig_traj_243.xlsx
@@ -999,22 +999,22 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.01720709547228782</v>
+        <v>0.03642717954281331</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C2" t="n">
         <v>-0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.04730042843192791</v>
+        <v>-0.06972293634865806</v>
       </c>
       <c r="E2" t="n">
-        <v>0.002052295138297554</v>
+        <v>-0.01652020775468693</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>-0</v>
@@ -1023,10 +1023,10 @@
         <v>-0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J2" t="n">
-        <v>0.02867181753036541</v>
+        <v>0.008729517739477157</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -1035,10 +1035,10 @@
         <v>-0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.006783586516577135</v>
+        <v>-0.05428603120921702</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.01173264113208584</v>
+        <v>-0.02360363080477972</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -1047,106 +1047,106 @@
         <v>-0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.008438760094107335</v>
+        <v>-0.03058502106434091</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>0.03412691072573807</v>
+        <v>-0.02844069431393963</v>
       </c>
       <c r="W2" t="n">
-        <v>0.08148592904569199</v>
+        <v>-0.006403922055077949</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA2" t="n">
         <v>-0</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0.05925239339256624</v>
+        <v>-0.03254628678847626</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
         <v>-0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.01355412607152697</v>
+        <v>0.0386707926381628</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.09746434992922172</v>
+        <v>0.08820445971707296</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>-0.01862454153288025</v>
+        <v>-0.01226214018728828</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN2" t="n">
-        <v>-0.02496742099186052</v>
+        <v>-0.1134110780278932</v>
       </c>
       <c r="AO2" t="n">
-        <v>-0.0858132223554073</v>
+        <v>0.0575013275239705</v>
       </c>
       <c r="AP2" t="n">
         <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.03703046872818438</v>
+        <v>-0.05446878733106211</v>
       </c>
       <c r="AU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW2" t="n">
-        <v>-0.07452219329730683</v>
+        <v>-0.2432759967517281</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.1539739451265189</v>
+        <v>-0.1123588198124954</v>
       </c>
       <c r="AY2" t="n">
         <v>-0</v>
@@ -1161,46 +1161,46 @@
         <v>-0</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.09303686334373516</v>
+        <v>0.2038593526715858</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF2" t="n">
-        <v>-0.01897182529809428</v>
+        <v>0.1577295761955973</v>
       </c>
       <c r="BG2" t="n">
-        <v>-0.01713696662735891</v>
+        <v>0.1300561089807079</v>
       </c>
       <c r="BH2" t="n">
         <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK2" t="n">
         <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.04651486549914551</v>
+        <v>0.04206340761131305</v>
       </c>
       <c r="BM2" t="n">
         <v>0</v>
       </c>
       <c r="BN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.02898909098044958</v>
+        <v>0.008699352248383455</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.1119218159732941</v>
+        <v>-0.1018518392918279</v>
       </c>
       <c r="BQ2" t="n">
         <v>0</v>
@@ -1209,94 +1209,94 @@
         <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU2" t="n">
-        <v>-0.001297500501931044</v>
+        <v>-0.09766446441509409</v>
       </c>
       <c r="BV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BW2" t="n">
         <v>-0</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.01803286767452541</v>
+        <v>-0.2429372218764551</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.103166075132843</v>
+        <v>-0.06410023553728036</v>
       </c>
       <c r="BZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB2" t="n">
         <v>0</v>
       </c>
       <c r="CC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD2" t="n">
-        <v>-0.002455696958476046</v>
+        <v>-0.03151343374055969</v>
       </c>
       <c r="CE2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CF2" t="n">
         <v>0</v>
       </c>
       <c r="CG2" t="n">
-        <v>-0.00558731652462223</v>
+        <v>0.09799194102411904</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.01174171427750151</v>
+        <v>0.01789056752265794</v>
       </c>
       <c r="CI2" t="n">
         <v>0</v>
       </c>
       <c r="CJ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK2" t="n">
         <v>0</v>
       </c>
       <c r="CL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM2" t="n">
-        <v>0.009585154085993574</v>
+        <v>0.009665575785091361</v>
       </c>
       <c r="CN2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CO2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.01588875573330542</v>
+        <v>-0.02912095785158515</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.02415734196202513</v>
+        <v>0.03697021559756609</v>
       </c>
       <c r="CR2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU2" t="n">
         <v>-0</v>
       </c>
       <c r="CV2" t="n">
-        <v>0.004478016581103843</v>
+        <v>-0.03009114744946511</v>
       </c>
       <c r="CW2" t="n">
         <v>-0</v>
@@ -1305,10 +1305,10 @@
         <v>-0</v>
       </c>
       <c r="CY2" t="n">
-        <v>0.02069264181035282</v>
+        <v>0.09368041627394406</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.02883714356122835</v>
+        <v>0.03233241098224496</v>
       </c>
       <c r="DA2" t="n">
         <v>-0</v>
@@ -1320,22 +1320,22 @@
         <v>-0</v>
       </c>
       <c r="DD2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE2" t="n">
-        <v>-0.009612699076101615</v>
+        <v>-0.01716806754357479</v>
       </c>
       <c r="DF2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DG2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.1355830400492995</v>
+        <v>0.08912463611790968</v>
       </c>
       <c r="DI2" t="n">
-        <v>-0.08837926703886571</v>
+        <v>-0.02295787207340564</v>
       </c>
       <c r="DJ2" t="n">
         <v>0</v>
@@ -1347,10 +1347,10 @@
         <v>0</v>
       </c>
       <c r="DM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN2" t="n">
-        <v>-0.007588174768674401</v>
+        <v>-0.08373951908586717</v>
       </c>
       <c r="DO2" t="n">
         <v>-0</v>
@@ -1359,16 +1359,16 @@
         <v>0</v>
       </c>
       <c r="DQ2" t="n">
-        <v>-0.02323548620398797</v>
+        <v>0.03733145489051629</v>
       </c>
       <c r="DR2" t="n">
-        <v>-0.07696550524383995</v>
+        <v>0.06489911131720263</v>
       </c>
       <c r="DS2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU2" t="n">
         <v>-0</v>
@@ -1377,76 +1377,76 @@
         <v>0</v>
       </c>
       <c r="DW2" t="n">
-        <v>-0.00315473780756032</v>
+        <v>0.07367369172916641</v>
       </c>
       <c r="DX2" t="n">
         <v>-0</v>
       </c>
       <c r="DY2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ2" t="n">
-        <v>-0.07916285869597549</v>
+        <v>0.07580169855670599</v>
       </c>
       <c r="EA2" t="n">
-        <v>0.005272824678598045</v>
+        <v>0.04008982112578077</v>
       </c>
       <c r="EB2" t="n">
         <v>0</v>
       </c>
       <c r="EC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF2" t="n">
-        <v>-0.0008348592136449349</v>
+        <v>-0.07069586889308514</v>
       </c>
       <c r="EG2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EH2" t="n">
         <v>0</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.01430509647092726</v>
+        <v>0.05856063682437101</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.05806990207935846</v>
+        <v>0.05152224269515335</v>
       </c>
       <c r="EK2" t="n">
         <v>0</v>
       </c>
       <c r="EL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM2" t="n">
         <v>0</v>
       </c>
       <c r="EN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO2" t="n">
-        <v>-0.02992212443786825</v>
+        <v>0.02112322568681692</v>
       </c>
       <c r="EP2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EQ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER2" t="n">
-        <v>0.02378926360419584</v>
+        <v>0.09742343409366412</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.06541123093438692</v>
+        <v>-0.001302889805905479</v>
       </c>
       <c r="ET2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU2" t="n">
         <v>0</v>
@@ -1458,19 +1458,19 @@
         <v>-0</v>
       </c>
       <c r="EX2" t="n">
-        <v>0.003345686173657754</v>
+        <v>-0.02274013240940201</v>
       </c>
       <c r="EY2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EZ2" t="n">
         <v>0</v>
       </c>
       <c r="FA2" t="n">
-        <v>0.01344095782736715</v>
+        <v>0.1334335286880359</v>
       </c>
       <c r="FB2" t="n">
-        <v>0.02043763997552751</v>
+        <v>0.02818939390696719</v>
       </c>
       <c r="FC2" t="n">
         <v>0</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="FF2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG2" t="n">
-        <v>-0.01558806318082757</v>
+        <v>0.006483736233295818</v>
       </c>
       <c r="FH2" t="n">
         <v>0</v>
@@ -1494,13 +1494,13 @@
         <v>-0</v>
       </c>
       <c r="FJ2" t="n">
-        <v>0.07725885371678497</v>
+        <v>0.08680820675119</v>
       </c>
       <c r="FK2" t="n">
-        <v>-0.09077299521997133</v>
+        <v>0.1188785373661655</v>
       </c>
       <c r="FL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM2" t="n">
         <v>-0</v>
@@ -1512,7 +1512,7 @@
         <v>-0</v>
       </c>
       <c r="FP2" t="n">
-        <v>0.006164893926639823</v>
+        <v>0.01257767818529067</v>
       </c>
       <c r="FQ2" t="n">
         <v>0</v>
@@ -1521,10 +1521,10 @@
         <v>-0</v>
       </c>
       <c r="FS2" t="n">
-        <v>-0.03089295523108242</v>
+        <v>0.1792835118839974</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.01576987555661315</v>
+        <v>0.05737745971149106</v>
       </c>
       <c r="FU2" t="n">
         <v>0</v>
@@ -1536,22 +1536,22 @@
         <v>0</v>
       </c>
       <c r="FX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY2" t="n">
-        <v>-0.001702983009483345</v>
+        <v>-0.02196025036724714</v>
       </c>
       <c r="FZ2" t="n">
         <v>0</v>
       </c>
       <c r="GA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB2" t="n">
-        <v>0.0117956656658099</v>
+        <v>0.1870384870806662</v>
       </c>
       <c r="GC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD2" t="n">
         <v>0</v>
@@ -2709,16 +2709,16 @@
         <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.2568543612326306</v>
+        <v>0.1333508142234649</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.07072877886087157</v>
+        <v>-0.05439120774768355</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.01453633327424071</v>
+        <v>-0.02469296497777191</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -2730,22 +2730,22 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1454210131144689</v>
+        <v>0.107362676624905</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.05489902178942812</v>
+        <v>-0.06040574101746417</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.01294621625032826</v>
+        <v>-0.04254777332529464</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -2763,70 +2763,70 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1009555584149974</v>
+        <v>0.02610870572138899</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.05983771100244027</v>
+        <v>-0.04822616855604982</v>
       </c>
       <c r="W5" t="n">
-        <v>0.05441196482686772</v>
+        <v>-0.06062770680781117</v>
       </c>
       <c r="X5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
         <v>-0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.04432014451801228</v>
+        <v>-0.0128389660464146</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.0005384614756722776</v>
+        <v>-0.131097602859284</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.01709806490981998</v>
+        <v>-0.0291042995078898</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
         <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.0361324642298417</v>
+        <v>0.06114020057189415</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.0678914455406979</v>
+        <v>-0.08871073477056161</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.04290993302262906</v>
+        <v>0.05439991527639335</v>
       </c>
       <c r="AP5" t="n">
         <v>0</v>
@@ -2835,61 +2835,61 @@
         <v>-0</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS5" t="n">
         <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.4457952707331587</v>
+        <v>0.2798437313937149</v>
       </c>
       <c r="AV5" t="n">
         <v>-0</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.009633695419559647</v>
+        <v>-0.06616382008804794</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.101475562834936</v>
+        <v>-0.1695919183444818</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC5" t="n">
         <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.07856160867638715</v>
+        <v>-0.0222123909542089</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.1548967524928643</v>
+        <v>-0.007042328137168029</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.1208096928303502</v>
+        <v>0.01098317033191792</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK5" t="n">
         <v>0</v>
@@ -2898,16 +2898,16 @@
         <v>-0</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.08132114020491003</v>
+        <v>0.01895714838954876</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.08785110425435499</v>
+        <v>0.02409688555988278</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.1266883866628938</v>
+        <v>0.05349635208077069</v>
       </c>
       <c r="BQ5" t="n">
         <v>-0</v>
@@ -2922,79 +2922,79 @@
         <v>-0</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.2111320070080372</v>
+        <v>0.1456292513548698</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0.03545580571011254</v>
+        <v>-0.1283557634509938</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.05142680013381701</v>
+        <v>-0.06123507233200421</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA5" t="n">
         <v>-0</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC5" t="n">
         <v>0</v>
       </c>
       <c r="CD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.1144756010796734</v>
+        <v>-0.1051233400555187</v>
       </c>
       <c r="CF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.01750894812702801</v>
+        <v>0.08641525478731614</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.02058119053319494</v>
+        <v>0.01909896270307937</v>
       </c>
       <c r="CI5" t="n">
         <v>-0</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK5" t="n">
         <v>0</v>
       </c>
       <c r="CL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM5" t="n">
         <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>-8.103759255529307e-05</v>
+        <v>0.003072724255725814</v>
       </c>
       <c r="CO5" t="n">
         <v>-0</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.003917702723322558</v>
+        <v>-0.007003074746624439</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.01298565759885731</v>
+        <v>-0.002789657977157437</v>
       </c>
       <c r="CR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT5" t="n">
         <v>0</v>
@@ -3003,19 +3003,19 @@
         <v>-0</v>
       </c>
       <c r="CV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.1020334484535813</v>
+        <v>-0.1060792492550329</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.05696547448469591</v>
+        <v>0.09649964417400009</v>
       </c>
       <c r="CZ5" t="n">
-        <v>-0.02736825830866337</v>
+        <v>0.02491859101162535</v>
       </c>
       <c r="DA5" t="n">
         <v>0</v>
@@ -3027,22 +3027,22 @@
         <v>-0</v>
       </c>
       <c r="DD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE5" t="n">
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.03514519372226782</v>
+        <v>-0.06186179400231349</v>
       </c>
       <c r="DG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.0816909654684724</v>
+        <v>0.009853020207934391</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.01976695313711738</v>
+        <v>-0.07717346644910494</v>
       </c>
       <c r="DJ5" t="n">
         <v>-0</v>
@@ -3054,25 +3054,25 @@
         <v>0</v>
       </c>
       <c r="DM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.07498991360167558</v>
+        <v>-0.05508978326679702</v>
       </c>
       <c r="DP5" t="n">
         <v>0</v>
       </c>
       <c r="DQ5" t="n">
-        <v>-0.005989301676870907</v>
+        <v>0.01030727048387228</v>
       </c>
       <c r="DR5" t="n">
-        <v>-0.04585071257810771</v>
+        <v>0.005055530596756769</v>
       </c>
       <c r="DS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT5" t="n">
         <v>-0</v>
@@ -3087,76 +3087,76 @@
         <v>-0</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.06792475117351628</v>
+        <v>-0.04561736727025366</v>
       </c>
       <c r="DY5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>-0.02360065761790696</v>
+        <v>0.07123189812551008</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.0007815582955062754</v>
+        <v>0.0326379380961555</v>
       </c>
       <c r="EB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.08718373506568633</v>
+        <v>-0.07237769389449225</v>
       </c>
       <c r="EH5" t="n">
         <v>-0</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.0214016074983573</v>
+        <v>0.06004087947767071</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.04203364012331771</v>
+        <v>0.03589416567557063</v>
       </c>
       <c r="EK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL5" t="n">
         <v>-0</v>
       </c>
       <c r="EM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO5" t="n">
         <v>0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.05225861018788792</v>
+        <v>-0.02614893356872949</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.04016199321304695</v>
+        <v>0.06542535754926876</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.00152306112881161</v>
+        <v>-0.01768710749268505</v>
       </c>
       <c r="ET5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV5" t="n">
         <v>0</v>
@@ -3165,46 +3165,46 @@
         <v>-0</v>
       </c>
       <c r="EX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.09769970561267689</v>
+        <v>-0.1164909647055029</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.02456125274467553</v>
+        <v>0.1178468974145647</v>
       </c>
       <c r="FB5" t="n">
-        <v>-0.01948373635469878</v>
+        <v>0.007663040886017792</v>
       </c>
       <c r="FC5" t="n">
         <v>-0</v>
       </c>
       <c r="FD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG5" t="n">
         <v>0</v>
       </c>
       <c r="FH5" t="n">
-        <v>-0.02152096084314175</v>
+        <v>0.09327738425628852</v>
       </c>
       <c r="FI5" t="n">
         <v>-0</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.02620990044666262</v>
+        <v>0.09083192624264938</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.006555326140354424</v>
+        <v>0.03949514006243344</v>
       </c>
       <c r="FL5" t="n">
         <v>-0</v>
@@ -3216,28 +3216,28 @@
         <v>-0</v>
       </c>
       <c r="FO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>-0.01279099905752969</v>
+        <v>0.04295154832188337</v>
       </c>
       <c r="FR5" t="n">
         <v>0</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.04359320393120833</v>
+        <v>0.1557627064561025</v>
       </c>
       <c r="FT5" t="n">
-        <v>-0.04772067903197435</v>
+        <v>-0.02499005395523241</v>
       </c>
       <c r="FU5" t="n">
         <v>-0</v>
       </c>
       <c r="FV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW5" t="n">
         <v>0</v>
@@ -3246,22 +3246,22 @@
         <v>0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.04460360095595166</v>
+        <v>-0.05721348393359261</v>
       </c>
       <c r="GA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB5" t="n">
-        <v>-0.07148917415227128</v>
+        <v>0.08311136914001926</v>
       </c>
       <c r="GC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE5" t="n">
         <v>-0</v>
@@ -3278,7 +3278,7 @@
         <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>0.05941400671657383</v>
+        <v>0.1398943044644647</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -3287,10 +3287,10 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.01540958628677235</v>
+        <v>-0.01157914955250763</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.02060761422634686</v>
+        <v>-0.07137136044689317</v>
       </c>
       <c r="G6" t="n">
         <v>-0</v>
@@ -3299,13 +3299,13 @@
         <v>-0</v>
       </c>
       <c r="I6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03791330849744347</v>
+        <v>0.1451244031638122</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -3314,64 +3314,64 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.01241617702117164</v>
+        <v>-0.04746203517841516</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.01421613578192648</v>
+        <v>-0.05141368840548297</v>
       </c>
       <c r="P6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.01220481651926991</v>
+        <v>0.07921731327738545</v>
       </c>
       <c r="U6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.004037940116326967</v>
+        <v>-0.06820036636010215</v>
       </c>
       <c r="X6" t="n">
-        <v>0.01303088004244116</v>
+        <v>-0.02972382506010975</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.01184358214960442</v>
+        <v>-0.002976686420355849</v>
       </c>
       <c r="AD6" t="n">
         <v>-0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.01045791630612842</v>
+        <v>-0.1558812635456229</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.00421872434797412</v>
+        <v>-0.01120076452368751</v>
       </c>
       <c r="AH6" t="n">
         <v>-0</v>
@@ -3380,13 +3380,13 @@
         <v>-0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
         <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.003986210029296527</v>
+        <v>0.06506411778518272</v>
       </c>
       <c r="AM6" t="n">
         <v>-0</v>
@@ -3395,25 +3395,25 @@
         <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.01625449241919918</v>
+        <v>-0.002888002731506491</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.01378836058254025</v>
+        <v>-0.04556458221933574</v>
       </c>
       <c r="AQ6" t="n">
         <v>-0</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS6" t="n">
         <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.08960561866212041</v>
+        <v>0.3477860588202641</v>
       </c>
       <c r="AV6" t="n">
         <v>-0</v>
@@ -3422,13 +3422,13 @@
         <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.006196483576929418</v>
+        <v>-0.1765580481410678</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.01858081040310278</v>
+        <v>-0.1241170584726165</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA6" t="n">
         <v>-0</v>
@@ -3440,7 +3440,7 @@
         <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.0250000687775013</v>
+        <v>-0.02434195108833545</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
@@ -3449,16 +3449,16 @@
         <v>0</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.06581140775578498</v>
+        <v>-0.0127497391843806</v>
       </c>
       <c r="BH6" t="n">
-        <v>-0.05247123261304147</v>
+        <v>-0.08340340377652622</v>
       </c>
       <c r="BI6" t="n">
         <v>0</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK6" t="n">
         <v>0</v>
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.03218249102935229</v>
+        <v>0.04635712491799324</v>
       </c>
       <c r="BN6" t="n">
         <v>-0</v>
@@ -3476,37 +3476,37 @@
         <v>-0</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.01882834370828882</v>
+        <v>0.09384516478437001</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.02115602771288829</v>
+        <v>0.05747560971262705</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS6" t="n">
         <v>-0</v>
       </c>
       <c r="BT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.03122973898646377</v>
+        <v>0.2004248431231547</v>
       </c>
       <c r="BW6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX6" t="n">
         <v>0</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.00651910714324539</v>
+        <v>-0.05410632254344886</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0.002964936025189064</v>
+        <v>-0.1375106439768399</v>
       </c>
       <c r="CA6" t="n">
         <v>-0</v>
@@ -3515,202 +3515,202 @@
         <v>-0</v>
       </c>
       <c r="CC6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.02308493429690457</v>
+        <v>-0.09699948003945624</v>
       </c>
       <c r="CF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG6" t="n">
         <v>-0</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.0009921390643612771</v>
+        <v>0.02441734906922041</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.01785944489989028</v>
+        <v>0.09033698909335619</v>
       </c>
       <c r="CJ6" t="n">
         <v>0</v>
       </c>
       <c r="CK6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL6" t="n">
         <v>0</v>
       </c>
       <c r="CM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.0004584355016765533</v>
+        <v>-0.004570899200842317</v>
       </c>
       <c r="CO6" t="n">
         <v>-0</v>
       </c>
       <c r="CP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ6" t="n">
-        <v>-0.0005650988745921655</v>
+        <v>-0.004757607949306777</v>
       </c>
       <c r="CR6" t="n">
-        <v>0.002040978741629576</v>
+        <v>-0.01126818397053971</v>
       </c>
       <c r="CS6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW6" t="n">
-        <v>-0.01552925361653226</v>
+        <v>-0.09830822174489463</v>
       </c>
       <c r="CX6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY6" t="n">
         <v>0</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.001466056964517457</v>
+        <v>0.01810918730135582</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.01895405060966631</v>
+        <v>0.1022968106225632</v>
       </c>
       <c r="DB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE6" t="n">
         <v>-0</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.01350693662742602</v>
+        <v>-0.03630574328086749</v>
       </c>
       <c r="DG6" t="n">
         <v>0</v>
       </c>
       <c r="DH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.02041845700869092</v>
+        <v>-0.03687370469500487</v>
       </c>
       <c r="DJ6" t="n">
-        <v>-0.004373832450851365</v>
+        <v>0.002638517518070811</v>
       </c>
       <c r="DK6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN6" t="n">
         <v>-0</v>
       </c>
       <c r="DO6" t="n">
-        <v>-0.001988292451863348</v>
+        <v>-0.01757040231266365</v>
       </c>
       <c r="DP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ6" t="n">
         <v>0</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.01387924240327595</v>
+        <v>-0.06307683737009534</v>
       </c>
       <c r="DS6" t="n">
-        <v>-0.009348654031697434</v>
+        <v>-0.01712977124530192</v>
       </c>
       <c r="DT6" t="n">
         <v>-0</v>
       </c>
       <c r="DU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX6" t="n">
-        <v>-0.02917948414354984</v>
+        <v>-0.06960754256783724</v>
       </c>
       <c r="DY6" t="n">
         <v>0</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.01579958249956461</v>
+        <v>0.02733956304392736</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.01205915456938285</v>
+        <v>0.06974716566034146</v>
       </c>
       <c r="EC6" t="n">
         <v>-0</v>
       </c>
       <c r="ED6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG6" t="n">
-        <v>-0.02398881548330636</v>
+        <v>-0.01771934879808964</v>
       </c>
       <c r="EH6" t="n">
         <v>-0</v>
       </c>
       <c r="EI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.008556925100015876</v>
+        <v>-0.002206881034998934</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.01507426309578756</v>
+        <v>0.02797620540204639</v>
       </c>
       <c r="EL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM6" t="n">
         <v>-0</v>
       </c>
       <c r="EN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP6" t="n">
-        <v>-0.01340548261656974</v>
+        <v>-0.0216668409192299</v>
       </c>
       <c r="EQ6" t="n">
         <v>-0</v>
@@ -3719,10 +3719,10 @@
         <v>-0</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.01152507291142987</v>
+        <v>-0.01792380187211991</v>
       </c>
       <c r="ET6" t="n">
-        <v>-0.001719075883829851</v>
+        <v>0.06173896825634031</v>
       </c>
       <c r="EU6" t="n">
         <v>0</v>
@@ -3731,31 +3731,31 @@
         <v>0</v>
       </c>
       <c r="EW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY6" t="n">
-        <v>-0.01582000119425891</v>
+        <v>-0.109008390155091</v>
       </c>
       <c r="EZ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA6" t="n">
         <v>-0</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.003596885381339192</v>
+        <v>0.003388691316005726</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.02370123352480092</v>
+        <v>0.07880934843056256</v>
       </c>
       <c r="FD6" t="n">
         <v>0</v>
       </c>
       <c r="FE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF6" t="n">
         <v>-0</v>
@@ -3764,25 +3764,25 @@
         <v>0</v>
       </c>
       <c r="FH6" t="n">
-        <v>-0.01994257063429896</v>
+        <v>0.1271539672546482</v>
       </c>
       <c r="FI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ6" t="n">
         <v>-0</v>
       </c>
       <c r="FK6" t="n">
-        <v>0.02291543115169448</v>
+        <v>-0.06994975665839165</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.01230589297746656</v>
+        <v>0.08614845765012456</v>
       </c>
       <c r="FM6" t="n">
         <v>0</v>
       </c>
       <c r="FN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO6" t="n">
         <v>0</v>
@@ -3791,7 +3791,7 @@
         <v>0</v>
       </c>
       <c r="FQ6" t="n">
-        <v>-0.0005489374222000092</v>
+        <v>0.05402001637697765</v>
       </c>
       <c r="FR6" t="n">
         <v>0</v>
@@ -3800,46 +3800,46 @@
         <v>-0</v>
       </c>
       <c r="FT6" t="n">
-        <v>-0.0177102964616271</v>
+        <v>-0.03582154793572224</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.005078816036053805</v>
+        <v>0.01536949768135894</v>
       </c>
       <c r="FV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ6" t="n">
-        <v>-0.001310865039648626</v>
+        <v>-0.02339394911638851</v>
       </c>
       <c r="GA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB6" t="n">
         <v>-0</v>
       </c>
       <c r="GC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD6" t="n">
-        <v>-0.01636827680731826</v>
+        <v>0.07921638581055314</v>
       </c>
       <c r="GE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF6" t="n">
         <v>-0</v>
       </c>
       <c r="GG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -3847,22 +3847,22 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.2537866312702725</v>
+        <v>0.1913433384722225</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.04961397724851137</v>
+        <v>-0.06432417995194202</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.04825441666313628</v>
+        <v>-0.0407040658496735</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -3874,16 +3874,16 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1574540843120492</v>
+        <v>0.1873768511468454</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.03562481523662205</v>
+        <v>-0.05879358608126272</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.03490978820443408</v>
+        <v>-0.07571439066483676</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -3901,70 +3901,70 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.07931924508318292</v>
+        <v>0.04589231372831248</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.03540462970523174</v>
+        <v>-0.03113156616951594</v>
       </c>
       <c r="W7" t="n">
-        <v>0.06432452889444486</v>
+        <v>-0.0704005549070022</v>
       </c>
       <c r="X7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
         <v>-0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.02267603049305261</v>
+        <v>-0.01490007092267936</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.01669396212702222</v>
+        <v>-0.134575764040771</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.005220467381315663</v>
+        <v>-0.02870106333105613</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.01058431728842851</v>
+        <v>0.08044649262243359</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0.04165385916277334</v>
+        <v>-0.07286911803202567</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.04001254954333256</v>
+        <v>0.06159362214124857</v>
       </c>
       <c r="AP7" t="n">
         <v>0</v>
@@ -3973,34 +3973,34 @@
         <v>-0</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS7" t="n">
         <v>0</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.4059268967038039</v>
+        <v>0.2606225526841412</v>
       </c>
       <c r="AV7" t="n">
         <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.03712845452817398</v>
+        <v>-0.06503329156140401</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.0554736869396807</v>
+        <v>-0.2356776903640495</v>
       </c>
       <c r="AY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
         <v>-0</v>
@@ -4009,25 +4009,25 @@
         <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.04654572725989747</v>
+        <v>0.003172755569678888</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>-0.1408653694785345</v>
+        <v>-0.03998996696598511</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.1189306953011155</v>
+        <v>0.008406303608108923</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
       </c>
       <c r="BI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK7" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>-0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.1099922337662752</v>
+        <v>0.008591877794443127</v>
       </c>
       <c r="BN7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.06173741789490112</v>
+        <v>0.03941152393230624</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.1278005372894237</v>
+        <v>0.07611586717620944</v>
       </c>
       <c r="BQ7" t="n">
         <v>-0</v>
@@ -4057,82 +4057,82 @@
         <v>-0</v>
       </c>
       <c r="BT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU7" t="n">
         <v>0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.1927928168289693</v>
+        <v>0.1554726245539866</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.00659066819075915</v>
+        <v>-0.09258671590982415</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.03230984868338774</v>
+        <v>-0.09013421185924382</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA7" t="n">
         <v>-0</v>
       </c>
       <c r="CB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD7" t="n">
         <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.09542635005070459</v>
+        <v>-0.1133199130282239</v>
       </c>
       <c r="CF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG7" t="n">
-        <v>-0.009210289658419812</v>
+        <v>0.09744988293657474</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.001539089253579752</v>
+        <v>0.02908154009202409</v>
       </c>
       <c r="CI7" t="n">
         <v>-0</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK7" t="n">
         <v>0</v>
       </c>
       <c r="CL7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM7" t="n">
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.001781198556638281</v>
+        <v>-0.006093327769649994</v>
       </c>
       <c r="CO7" t="n">
         <v>-0</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.003454931697118517</v>
+        <v>-0.008358896375539226</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.002789828966866228</v>
+        <v>0.002294621351767123</v>
       </c>
       <c r="CR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT7" t="n">
         <v>0</v>
@@ -4141,19 +4141,19 @@
         <v>-0</v>
       </c>
       <c r="CV7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.07103145851941361</v>
+        <v>-0.1148179207064052</v>
       </c>
       <c r="CX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.02860618777326679</v>
+        <v>0.1100582681020266</v>
       </c>
       <c r="CZ7" t="n">
-        <v>-0.008440003291297599</v>
+        <v>0.03831661841963793</v>
       </c>
       <c r="DA7" t="n">
         <v>0</v>
@@ -4162,25 +4162,25 @@
         <v>0</v>
       </c>
       <c r="DC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.02624895969771109</v>
+        <v>-0.06662836417581178</v>
       </c>
       <c r="DG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.05522839552856176</v>
+        <v>-0.001207462755469529</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.0170505529799228</v>
+        <v>-0.03571615655096217</v>
       </c>
       <c r="DJ7" t="n">
         <v>-0</v>
@@ -4192,31 +4192,31 @@
         <v>0</v>
       </c>
       <c r="DM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.08895831383673426</v>
+        <v>-0.0546679113185757</v>
       </c>
       <c r="DP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>-0.01656265957648866</v>
+        <v>-0.04782084211817288</v>
       </c>
       <c r="DR7" t="n">
-        <v>-0.03721128066633555</v>
+        <v>-0.05437731875005908</v>
       </c>
       <c r="DS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT7" t="n">
         <v>-0</v>
       </c>
       <c r="DU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV7" t="n">
         <v>0</v>
@@ -4225,16 +4225,16 @@
         <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>-0.06078186710608073</v>
+        <v>-0.01416448063911082</v>
       </c>
       <c r="DY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>-0.04124255762769985</v>
+        <v>0.05550512004973138</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.005655117329051819</v>
+        <v>0.01184516071461773</v>
       </c>
       <c r="EB7" t="n">
         <v>-0</v>
@@ -4243,58 +4243,58 @@
         <v>-0</v>
       </c>
       <c r="ED7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.07570244030469159</v>
+        <v>-0.06768616006622924</v>
       </c>
       <c r="EH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI7" t="n">
-        <v>-0.002131980540546732</v>
+        <v>0.06737681918137406</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.06204353559522383</v>
+        <v>0.0473301776012524</v>
       </c>
       <c r="EK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL7" t="n">
         <v>-0</v>
       </c>
       <c r="EM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN7" t="n">
         <v>-0</v>
       </c>
       <c r="EO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.01064985971146341</v>
+        <v>-0.05088338469141345</v>
       </c>
       <c r="EQ7" t="n">
         <v>0</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.01764835388592073</v>
+        <v>0.04486411263983033</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.0255650746803939</v>
+        <v>0.02231074965588747</v>
       </c>
       <c r="ET7" t="n">
         <v>-0</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV7" t="n">
         <v>0</v>
@@ -4306,16 +4306,16 @@
         <v>-0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.06815437734417872</v>
+        <v>-0.1214605637667861</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA7" t="n">
-        <v>-0.0002830842543334325</v>
+        <v>0.1279184172047978</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.01086075013050436</v>
+        <v>0.01475829423222307</v>
       </c>
       <c r="FC7" t="n">
         <v>-0</v>
@@ -4324,25 +4324,25 @@
         <v>0</v>
       </c>
       <c r="FE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG7" t="n">
         <v>0</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.04150801066692208</v>
+        <v>0.1208724801250574</v>
       </c>
       <c r="FI7" t="n">
         <v>-0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.01002956301223026</v>
+        <v>0.0890900495232224</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.005897153011662478</v>
+        <v>-0.001901380416883676</v>
       </c>
       <c r="FL7" t="n">
         <v>-0</v>
@@ -4351,31 +4351,31 @@
         <v>0</v>
       </c>
       <c r="FN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0.03154583850752581</v>
+        <v>0.03337148438523926</v>
       </c>
       <c r="FR7" t="n">
         <v>0</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.0532103331734006</v>
+        <v>0.1768235988473886</v>
       </c>
       <c r="FT7" t="n">
-        <v>-0.06406988471780828</v>
+        <v>-0.03913677609644083</v>
       </c>
       <c r="FU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW7" t="n">
         <v>0</v>
@@ -4384,31 +4384,31 @@
         <v>0</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.0415845283475323</v>
+        <v>-0.04279567658610504</v>
       </c>
       <c r="GA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB7" t="n">
-        <v>-0.07185674434994309</v>
+        <v>0.04208748033640444</v>
       </c>
       <c r="GC7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF7" t="n">
         <v>0</v>
       </c>
       <c r="GG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -4416,7 +4416,7 @@
         <v>0</v>
       </c>
       <c r="B8" t="n">
-        <v>0.1189080745086982</v>
+        <v>0.1873209370307486</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -4425,13 +4425,13 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.02718304330996373</v>
+        <v>0.01300653595206851</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.05977742534028958</v>
+        <v>-0.1468869805458244</v>
       </c>
       <c r="G8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>-0</v>
@@ -4440,10 +4440,10 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.08585159398145173</v>
+        <v>0.2045427913960607</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -4452,67 +4452,67 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.007901788865117622</v>
+        <v>-0.06072075586488782</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.04139062674179107</v>
+        <v>-0.1243297632176035</v>
       </c>
       <c r="P8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>-0</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.02312011616103813</v>
+        <v>0.08546856940460197</v>
       </c>
       <c r="U8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.03634041901626187</v>
+        <v>-0.05157085535418538</v>
       </c>
       <c r="X8" t="n">
-        <v>0.00818767813448151</v>
+        <v>-0.05288756289731977</v>
       </c>
       <c r="Y8" t="n">
         <v>-0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB8" t="n">
         <v>-0</v>
       </c>
       <c r="AC8" t="n">
-        <v>-0.0009625298704868476</v>
+        <v>-0.0196045088852774</v>
       </c>
       <c r="AD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.004629772916004128</v>
+        <v>-0.1010432863010257</v>
       </c>
       <c r="AG8" t="n">
-        <v>-0.009855466757474288</v>
+        <v>0.05384244120828718</v>
       </c>
       <c r="AH8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>-0</v>
@@ -4524,19 +4524,19 @@
         <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.02844326168093931</v>
+        <v>0.1127630447983892</v>
       </c>
       <c r="AM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>-0.01032703629393569</v>
+        <v>0.01222945560084891</v>
       </c>
       <c r="AP8" t="n">
-        <v>-0.03994661483022328</v>
+        <v>-0.0713528172740482</v>
       </c>
       <c r="AQ8" t="n">
         <v>-0</v>
@@ -4548,91 +4548,91 @@
         <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.1420307763901036</v>
+        <v>0.4988306331238241</v>
       </c>
       <c r="AV8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW8" t="n">
         <v>0</v>
       </c>
       <c r="AX8" t="n">
-        <v>-0.05648660489303407</v>
+        <v>-0.1824485938987704</v>
       </c>
       <c r="AY8" t="n">
-        <v>-0.07394965413530043</v>
+        <v>-0.1787080708181836</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC8" t="n">
         <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.04921082707053887</v>
+        <v>-0.0911637300600607</v>
       </c>
       <c r="BE8" t="n">
         <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG8" t="n">
-        <v>-0.02746864258624076</v>
+        <v>-0.004384427349480527</v>
       </c>
       <c r="BH8" t="n">
-        <v>-0.04639745097381796</v>
+        <v>-0.09586061336350468</v>
       </c>
       <c r="BI8" t="n">
         <v>0</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.04985358062100945</v>
+        <v>0.09653770632670747</v>
       </c>
       <c r="BN8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.02668722524292261</v>
+        <v>0.04002700307014929</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.01615459123519948</v>
+        <v>0.07261530408717094</v>
       </c>
       <c r="BR8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS8" t="n">
         <v>0</v>
       </c>
       <c r="BT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.07776708584325823</v>
+        <v>0.2753031195028953</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
@@ -4641,37 +4641,37 @@
         <v>0</v>
       </c>
       <c r="BY8" t="n">
-        <v>-0.03565850228275393</v>
+        <v>-0.07353026290234045</v>
       </c>
       <c r="BZ8" t="n">
-        <v>-0.02826783512109161</v>
+        <v>-0.1839000181709978</v>
       </c>
       <c r="CA8" t="n">
         <v>-0</v>
       </c>
       <c r="CB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE8" t="n">
-        <v>-0.03573167018372014</v>
+        <v>-0.1246654185725395</v>
       </c>
       <c r="CF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG8" t="n">
         <v>-0</v>
       </c>
       <c r="CH8" t="n">
-        <v>-0.005778094588246368</v>
+        <v>0.01642821627101466</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.03380931734631901</v>
+        <v>0.08981379396202127</v>
       </c>
       <c r="CJ8" t="n">
         <v>-0</v>
@@ -4680,52 +4680,52 @@
         <v>0</v>
       </c>
       <c r="CL8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM8" t="n">
         <v>0</v>
       </c>
       <c r="CN8" t="n">
-        <v>-0.0006225278655990108</v>
+        <v>-0.03700849541072412</v>
       </c>
       <c r="CO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.0005968818610915542</v>
+        <v>0.01864037419379815</v>
       </c>
       <c r="CR8" t="n">
-        <v>0.001739340220446011</v>
+        <v>0.0003171788247645382</v>
       </c>
       <c r="CS8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT8" t="n">
         <v>-0</v>
       </c>
       <c r="CU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV8" t="n">
         <v>-0</v>
       </c>
       <c r="CW8" t="n">
-        <v>-0.03053585207700382</v>
+        <v>-0.1162830264331022</v>
       </c>
       <c r="CX8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY8" t="n">
         <v>0</v>
       </c>
       <c r="CZ8" t="n">
-        <v>-0.00268003868448679</v>
+        <v>0.01141564383900411</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.03897325388939985</v>
+        <v>0.11016234064352</v>
       </c>
       <c r="DB8" t="n">
         <v>0</v>
@@ -4740,7 +4740,7 @@
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>-0.04580990757737437</v>
+        <v>-0.1215586795501377</v>
       </c>
       <c r="DG8" t="n">
         <v>0</v>
@@ -4749,25 +4749,25 @@
         <v>-0</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.06129352253348469</v>
+        <v>-0.0237363886678547</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.0006151487334720656</v>
+        <v>0.02203605958748772</v>
       </c>
       <c r="DK8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL8" t="n">
         <v>0</v>
       </c>
       <c r="DM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>-0.01567187773431611</v>
+        <v>-0.09542514650166807</v>
       </c>
       <c r="DP8" t="n">
         <v>0</v>
@@ -4776,37 +4776,37 @@
         <v>0</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.01914924617560206</v>
+        <v>0.009429270162906829</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.004192642200016228</v>
+        <v>0.1577983852295752</v>
       </c>
       <c r="DT8" t="n">
         <v>-0</v>
       </c>
       <c r="DU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV8" t="n">
         <v>0</v>
       </c>
       <c r="DW8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX8" t="n">
-        <v>-0.0418839173363631</v>
+        <v>-0.07968197188507524</v>
       </c>
       <c r="DY8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.01609446059128455</v>
+        <v>0.06853547951054943</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.02927097094429964</v>
+        <v>0.02940718104823475</v>
       </c>
       <c r="EC8" t="n">
         <v>-0</v>
@@ -4815,55 +4815,55 @@
         <v>0</v>
       </c>
       <c r="EE8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF8" t="n">
         <v>0</v>
       </c>
       <c r="EG8" t="n">
-        <v>-0.02747421758142719</v>
+        <v>-0.06220405917698915</v>
       </c>
       <c r="EH8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.01061003864232607</v>
+        <v>-0.03880203666487691</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.03602328410936323</v>
+        <v>0.0220714290622941</v>
       </c>
       <c r="EL8" t="n">
         <v>-0</v>
       </c>
       <c r="EM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO8" t="n">
         <v>0</v>
       </c>
       <c r="EP8" t="n">
-        <v>-0.02581372830057888</v>
+        <v>-0.0236233781312809</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES8" t="n">
-        <v>-0.01489238014802006</v>
+        <v>-0.0786383490673804</v>
       </c>
       <c r="ET8" t="n">
-        <v>-0.0002200934954572141</v>
+        <v>-0.00121138553606047</v>
       </c>
       <c r="EU8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV8" t="n">
         <v>0</v>
@@ -4875,106 +4875,106 @@
         <v>0</v>
       </c>
       <c r="EY8" t="n">
-        <v>-0.03128137913871103</v>
+        <v>-0.1383374867793414</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA8" t="n">
         <v>-0</v>
       </c>
       <c r="FB8" t="n">
-        <v>-0.0004016919558901625</v>
+        <v>-0.001097120928433899</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.03890655914819156</v>
+        <v>0.1027349250253289</v>
       </c>
       <c r="FD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE8" t="n">
         <v>0</v>
       </c>
       <c r="FF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG8" t="n">
         <v>0</v>
       </c>
       <c r="FH8" t="n">
-        <v>-0.02287897090956699</v>
+        <v>0.07192551115732405</v>
       </c>
       <c r="FI8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ8" t="n">
         <v>-0</v>
       </c>
       <c r="FK8" t="n">
-        <v>0.01239353301558893</v>
+        <v>-0.02594086038789261</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.02529373203734899</v>
+        <v>0.07490036104176476</v>
       </c>
       <c r="FM8" t="n">
         <v>0</v>
       </c>
       <c r="FN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO8" t="n">
         <v>0</v>
       </c>
       <c r="FP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ8" t="n">
-        <v>-0.009690299195433927</v>
+        <v>0.07678167137819755</v>
       </c>
       <c r="FR8" t="n">
         <v>-0</v>
       </c>
       <c r="FS8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FT8" t="n">
-        <v>-0.02838568015710879</v>
+        <v>-0.04480555844840879</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.02487169362083928</v>
+        <v>0.009931718228570545</v>
       </c>
       <c r="FV8" t="n">
         <v>-0</v>
       </c>
       <c r="FW8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ8" t="n">
-        <v>0.006219374501421094</v>
+        <v>-0.02686396687729217</v>
       </c>
       <c r="GA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB8" t="n">
         <v>-0</v>
       </c>
       <c r="GC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD8" t="n">
-        <v>-0.01958278467357271</v>
+        <v>0.0987252737397029</v>
       </c>
       <c r="GE8" t="n">
         <v>-0</v>
       </c>
       <c r="GF8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG8" t="n">
         <v>-0</v>
@@ -4985,7 +4985,7 @@
         <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.098589737730975</v>
+        <v>0.2569134810601393</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -4994,10 +4994,10 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.03716882124529888</v>
+        <v>-0.04996567402448836</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.05889402576708862</v>
+        <v>-0.1671262038762914</v>
       </c>
       <c r="G9" t="n">
         <v>-0</v>
@@ -5012,7 +5012,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.07591009000613824</v>
+        <v>0.2973857478324867</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -5021,64 +5021,64 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.02526441669601166</v>
+        <v>-0.1429194203941479</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.02897242378515327</v>
+        <v>-0.101964814769703</v>
       </c>
       <c r="P9" t="n">
         <v>-0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.01308287818657964</v>
+        <v>0.111291574325984</v>
       </c>
       <c r="U9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.01148623688754034</v>
+        <v>-0.1132115276314134</v>
       </c>
       <c r="X9" t="n">
-        <v>0.01531570970063306</v>
+        <v>-0.01774981785046731</v>
       </c>
       <c r="Y9" t="n">
         <v>-0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.0007722488823694022</v>
+        <v>-0.02138502215932248</v>
       </c>
       <c r="AD9" t="n">
         <v>-0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.009697745314079289</v>
+        <v>-0.2486005627568414</v>
       </c>
       <c r="AG9" t="n">
-        <v>-0.007242541824408706</v>
+        <v>0.02869287168354755</v>
       </c>
       <c r="AH9" t="n">
         <v>-0</v>
@@ -5093,7 +5093,7 @@
         <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.009657181753325368</v>
+        <v>0.06664978545866765</v>
       </c>
       <c r="AM9" t="n">
         <v>-0</v>
@@ -5102,10 +5102,10 @@
         <v>0</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.0164482372777186</v>
+        <v>-0.02820867137892817</v>
       </c>
       <c r="AP9" t="n">
-        <v>-0.01402000908131821</v>
+        <v>-0.01865340901757667</v>
       </c>
       <c r="AQ9" t="n">
         <v>-0</v>
@@ -5120,7 +5120,7 @@
         <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.1115342192350542</v>
+        <v>0.4886035892029876</v>
       </c>
       <c r="AV9" t="n">
         <v>-0</v>
@@ -5129,10 +5129,10 @@
         <v>0</v>
       </c>
       <c r="AX9" t="n">
-        <v>-0.03806562900629869</v>
+        <v>-0.2942647904587021</v>
       </c>
       <c r="AY9" t="n">
-        <v>-0.04875157598315774</v>
+        <v>-0.2011610222265792</v>
       </c>
       <c r="AZ9" t="n">
         <v>-0</v>
@@ -5147,7 +5147,7 @@
         <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.03627771225050603</v>
+        <v>-0.04072577487320504</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
@@ -5156,25 +5156,25 @@
         <v>0</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.06671482257130028</v>
+        <v>-0.01740349125500761</v>
       </c>
       <c r="BH9" t="n">
-        <v>-0.05611205330187267</v>
+        <v>-0.1122587431834512</v>
       </c>
       <c r="BI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK9" t="n">
         <v>0</v>
       </c>
       <c r="BL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.03853905649338467</v>
+        <v>0.06363294528741466</v>
       </c>
       <c r="BN9" t="n">
         <v>-0</v>
@@ -5183,13 +5183,13 @@
         <v>-0</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.02364058539047298</v>
+        <v>0.0994240193468147</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.01717465966608096</v>
+        <v>0.05824527627649526</v>
       </c>
       <c r="BR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS9" t="n">
         <v>-0</v>
@@ -5198,10 +5198,10 @@
         <v>0</v>
       </c>
       <c r="BU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.05380420809177421</v>
+        <v>0.2971257762805021</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
@@ -5210,10 +5210,10 @@
         <v>0</v>
       </c>
       <c r="BY9" t="n">
-        <v>-0.01849187197016208</v>
+        <v>-0.09575725226005227</v>
       </c>
       <c r="BZ9" t="n">
-        <v>-0.009626130295333645</v>
+        <v>-0.1069002303489354</v>
       </c>
       <c r="CA9" t="n">
         <v>-0</v>
@@ -5222,148 +5222,148 @@
         <v>-0</v>
       </c>
       <c r="CC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0.02762513005570845</v>
+        <v>-0.1273055419787933</v>
       </c>
       <c r="CF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG9" t="n">
         <v>-0</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.002012564282799612</v>
+        <v>0.036608427861873</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.02612644073259819</v>
+        <v>0.1000573649336454</v>
       </c>
       <c r="CJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL9" t="n">
         <v>0</v>
       </c>
       <c r="CM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.001572324596117162</v>
+        <v>-0.03914289917811564</v>
       </c>
       <c r="CO9" t="n">
         <v>-0</v>
       </c>
       <c r="CP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.00365336446598921</v>
+        <v>0.02799775514594221</v>
       </c>
       <c r="CR9" t="n">
-        <v>-0.00551051687141719</v>
+        <v>0.03078430432487615</v>
       </c>
       <c r="CS9" t="n">
         <v>-0</v>
       </c>
       <c r="CT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU9" t="n">
         <v>-0</v>
       </c>
       <c r="CV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW9" t="n">
-        <v>-0.02032286390559992</v>
+        <v>-0.1295213828205139</v>
       </c>
       <c r="CX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY9" t="n">
         <v>0</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.006837802213101968</v>
+        <v>0.02992199786386755</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.02882748845648164</v>
+        <v>0.1261916086782875</v>
       </c>
       <c r="DB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC9" t="n">
         <v>-0</v>
       </c>
       <c r="DD9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>-0.03345801405159488</v>
+        <v>-0.07254983405776685</v>
       </c>
       <c r="DG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.03608122934416567</v>
+        <v>-0.138139957115347</v>
       </c>
       <c r="DJ9" t="n">
-        <v>-0.0009048471383805738</v>
+        <v>0.03537006666583684</v>
       </c>
       <c r="DK9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN9" t="n">
         <v>-0</v>
       </c>
       <c r="DO9" t="n">
-        <v>-0.00690845174317941</v>
+        <v>-0.01626688213196711</v>
       </c>
       <c r="DP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.004166525402938957</v>
+        <v>-0.07717182827032279</v>
       </c>
       <c r="DS9" t="n">
-        <v>-0.006955147207822115</v>
+        <v>0.0294389340505027</v>
       </c>
       <c r="DT9" t="n">
         <v>-0</v>
       </c>
       <c r="DU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW9" t="n">
         <v>0</v>
       </c>
       <c r="DX9" t="n">
-        <v>-0.02764588040787757</v>
+        <v>-0.05709606740463781</v>
       </c>
       <c r="DY9" t="n">
         <v>0</v>
@@ -5372,10 +5372,10 @@
         <v>-0</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.0187381655148169</v>
+        <v>0.03690828654578876</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.02034467008597319</v>
+        <v>0.09990337958433256</v>
       </c>
       <c r="EC9" t="n">
         <v>-0</v>
@@ -5384,28 +5384,28 @@
         <v>0</v>
       </c>
       <c r="EE9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG9" t="n">
-        <v>-0.02781516952107855</v>
+        <v>-0.04407154335092583</v>
       </c>
       <c r="EH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI9" t="n">
         <v>0</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.01328962260646212</v>
+        <v>0.008587456503424311</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.0304176700423284</v>
+        <v>0.03362573414211575</v>
       </c>
       <c r="EL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM9" t="n">
         <v>-0</v>
@@ -5414,22 +5414,22 @@
         <v>0</v>
       </c>
       <c r="EO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP9" t="n">
-        <v>-0.013018733381946</v>
+        <v>-0.01215493688323225</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.01817494190107361</v>
+        <v>-0.02788114765804464</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.0008270683631312054</v>
+        <v>0.1129533598989842</v>
       </c>
       <c r="EU9" t="n">
         <v>0</v>
@@ -5438,13 +5438,13 @@
         <v>0</v>
       </c>
       <c r="EW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY9" t="n">
-        <v>-0.01948476015417681</v>
+        <v>-0.1442092416608852</v>
       </c>
       <c r="EZ9" t="n">
         <v>-0</v>
@@ -5453,43 +5453,43 @@
         <v>-0</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.008674003653532616</v>
+        <v>0.005505974783133329</v>
       </c>
       <c r="FC9" t="n">
-        <v>0.03110559423755292</v>
+        <v>0.09102578037579066</v>
       </c>
       <c r="FD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE9" t="n">
         <v>-0</v>
       </c>
       <c r="FF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG9" t="n">
         <v>0</v>
       </c>
       <c r="FH9" t="n">
-        <v>-0.01444319140441395</v>
+        <v>0.1971432346126029</v>
       </c>
       <c r="FI9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ9" t="n">
         <v>-0</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.01711024059670139</v>
+        <v>-0.0615064974149453</v>
       </c>
       <c r="FL9" t="n">
-        <v>0.01351874446343366</v>
+        <v>0.1277354737487042</v>
       </c>
       <c r="FM9" t="n">
         <v>0</v>
       </c>
       <c r="FN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO9" t="n">
         <v>0</v>
@@ -5498,55 +5498,55 @@
         <v>0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0.005266550371329591</v>
+        <v>0.06020563300667109</v>
       </c>
       <c r="FR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS9" t="n">
         <v>-0</v>
       </c>
       <c r="FT9" t="n">
-        <v>-0.0232812253095729</v>
+        <v>-0.0796384662859754</v>
       </c>
       <c r="FU9" t="n">
-        <v>0.00138062191346152</v>
+        <v>-0.09052998218412588</v>
       </c>
       <c r="FV9" t="n">
         <v>-0</v>
       </c>
       <c r="FW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.004166469481758102</v>
+        <v>-0.02240047971385015</v>
       </c>
       <c r="GA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB9" t="n">
         <v>-0</v>
       </c>
       <c r="GC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD9" t="n">
-        <v>-0.005889418146849242</v>
+        <v>0.1257982350161765</v>
       </c>
       <c r="GE9" t="n">
         <v>-0</v>
       </c>
       <c r="GF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -5554,22 +5554,22 @@
         <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>0.279124241643521</v>
+        <v>0.2607855320664335</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.06332259382534795</v>
+        <v>-0.1277286660224378</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.02762894846112073</v>
+        <v>-0.02845290759022768</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H10" t="n">
         <v>-0</v>
@@ -5581,22 +5581,22 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1907162918675416</v>
+        <v>0.2525698551695956</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.03652675361592649</v>
+        <v>-0.08000322192783196</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.03296570930158157</v>
+        <v>-0.06021094162698017</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -5608,70 +5608,70 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0842227134110114</v>
+        <v>0.02952208681713724</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V10" t="n">
-        <v>0.0002229368255991902</v>
+        <v>-0.01362600975602395</v>
       </c>
       <c r="W10" t="n">
-        <v>0.06514595656644362</v>
+        <v>-0.08831813211798209</v>
       </c>
       <c r="X10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
         <v>-0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.1259942104877981</v>
+        <v>-0.0314275690103231</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0.04420925084468882</v>
+        <v>-0.131166051263555</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.07848257797210868</v>
+        <v>-0.07831268413740101</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.02155216130396037</v>
+        <v>0.09973988431581668</v>
       </c>
       <c r="AM10" t="n">
         <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>-0.06807415932470212</v>
+        <v>-0.09225620850704286</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.03827357410075978</v>
+        <v>-0.003269200467380768</v>
       </c>
       <c r="AP10" t="n">
         <v>0</v>
@@ -5680,7 +5680,7 @@
         <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS10" t="n">
         <v>0</v>
@@ -5689,16 +5689,16 @@
         <v>-0</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.3492257278969247</v>
+        <v>0.2834478509452543</v>
       </c>
       <c r="AV10" t="n">
         <v>-0</v>
       </c>
       <c r="AW10" t="n">
-        <v>-0.00355701222424841</v>
+        <v>-0.2276768950889399</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.1345038130050455</v>
+        <v>-0.3405049030639589</v>
       </c>
       <c r="AY10" t="n">
         <v>-0</v>
@@ -5707,25 +5707,25 @@
         <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
         <v>-0</v>
       </c>
       <c r="BC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.03300920246290733</v>
+        <v>-0.01853609476384975</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>-0.05581374663042713</v>
+        <v>-0.02805605870965416</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.1735676531394212</v>
+        <v>0.05882606193369962</v>
       </c>
       <c r="BH10" t="n">
         <v>0</v>
@@ -5734,7 +5734,7 @@
         <v>-0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK10" t="n">
         <v>0</v>
@@ -5743,157 +5743,157 @@
         <v>-0</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.02978691146499432</v>
+        <v>0.02726152925015494</v>
       </c>
       <c r="BN10" t="n">
         <v>-0</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.09825332270577748</v>
+        <v>0.08614738276335838</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.0941963944260592</v>
+        <v>-0.006540301328475549</v>
       </c>
       <c r="BQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS10" t="n">
         <v>-0</v>
       </c>
       <c r="BT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU10" t="n">
         <v>0</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.197072476710902</v>
+        <v>0.2188366240602</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.01681565687068927</v>
+        <v>-0.1361031331302198</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.06166973723403793</v>
+        <v>-0.1150034042495716</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD10" t="n">
         <v>-0</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0.08767611171470337</v>
+        <v>-0.1213403971189885</v>
       </c>
       <c r="CF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.01295776117052723</v>
+        <v>0.1625167353974255</v>
       </c>
       <c r="CH10" t="n">
-        <v>-0.006527881850666439</v>
+        <v>0.01060618103704693</v>
       </c>
       <c r="CI10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK10" t="n">
         <v>0</v>
       </c>
       <c r="CL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM10" t="n">
         <v>0</v>
       </c>
       <c r="CN10" t="n">
-        <v>-0.01083110329922135</v>
+        <v>-0.02281401878543514</v>
       </c>
       <c r="CO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP10" t="n">
-        <v>-0.01425007821702101</v>
+        <v>0.02928192154939037</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.0197793589575065</v>
+        <v>0.03215251237194807</v>
       </c>
       <c r="CR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU10" t="n">
         <v>-0</v>
       </c>
       <c r="CV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW10" t="n">
-        <v>-0.07254481306032003</v>
+        <v>-0.1153926062500594</v>
       </c>
       <c r="CX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.03540277116295626</v>
+        <v>0.1702903923377896</v>
       </c>
       <c r="CZ10" t="n">
-        <v>-0.007749252218819924</v>
+        <v>0.01963770231055263</v>
       </c>
       <c r="DA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC10" t="n">
         <v>-0</v>
       </c>
       <c r="DD10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE10" t="n">
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0.01552554433418465</v>
+        <v>-0.07395309837329928</v>
       </c>
       <c r="DG10" t="n">
         <v>0</v>
       </c>
       <c r="DH10" t="n">
-        <v>-0.0003104113852679621</v>
+        <v>-0.01167830502688583</v>
       </c>
       <c r="DI10" t="n">
-        <v>-0.0003425891049277837</v>
+        <v>-0.1012014110814988</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL10" t="n">
         <v>0</v>
@@ -5902,25 +5902,25 @@
         <v>0</v>
       </c>
       <c r="DN10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>-0.06000578200483908</v>
+        <v>-0.04753778059785547</v>
       </c>
       <c r="DP10" t="n">
         <v>-0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>-0.06455456560740098</v>
+        <v>0.07843442099962625</v>
       </c>
       <c r="DR10" t="n">
-        <v>-0.06722639862900112</v>
+        <v>-0.0303886641016366</v>
       </c>
       <c r="DS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU10" t="n">
         <v>-0</v>
@@ -5929,19 +5929,19 @@
         <v>0</v>
       </c>
       <c r="DW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX10" t="n">
-        <v>-0.01088176422508598</v>
+        <v>0.02454811488022736</v>
       </c>
       <c r="DY10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ10" t="n">
-        <v>-0.01867734357225099</v>
+        <v>0.06439306347597153</v>
       </c>
       <c r="EA10" t="n">
-        <v>-0.005377033227939417</v>
+        <v>0.01104268911710778</v>
       </c>
       <c r="EB10" t="n">
         <v>0</v>
@@ -5950,58 +5950,58 @@
         <v>0</v>
       </c>
       <c r="ED10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF10" t="n">
         <v>0</v>
       </c>
       <c r="EG10" t="n">
-        <v>-0.05229549131452736</v>
+        <v>-0.07853482181913279</v>
       </c>
       <c r="EH10" t="n">
         <v>0</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.02704670919230993</v>
+        <v>0.1262159553382023</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.09251821182971544</v>
+        <v>0.02347434112177466</v>
       </c>
       <c r="EK10" t="n">
         <v>0</v>
       </c>
       <c r="EL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP10" t="n">
-        <v>-0.08152338177589474</v>
+        <v>-0.06807772672111304</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER10" t="n">
-        <v>-0.08667893894024714</v>
+        <v>-0.08378375591723734</v>
       </c>
       <c r="ES10" t="n">
-        <v>-0.01626069881236129</v>
+        <v>-0.03754090568641558</v>
       </c>
       <c r="ET10" t="n">
         <v>-0</v>
       </c>
       <c r="EU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV10" t="n">
         <v>0</v>
@@ -6010,25 +6010,25 @@
         <v>-0</v>
       </c>
       <c r="EX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0.07769133107128863</v>
+        <v>-0.1337854538083636</v>
       </c>
       <c r="EZ10" t="n">
         <v>-0</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.02266998334626571</v>
+        <v>0.1865418537922259</v>
       </c>
       <c r="FB10" t="n">
-        <v>-0.01028185361448744</v>
+        <v>0.0006863028102488193</v>
       </c>
       <c r="FC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE10" t="n">
         <v>0</v>
@@ -6040,49 +6040,49 @@
         <v>0</v>
       </c>
       <c r="FH10" t="n">
-        <v>-0.01051144063389798</v>
+        <v>0.1426711393867934</v>
       </c>
       <c r="FI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.04748965459258143</v>
+        <v>0.1464844067872841</v>
       </c>
       <c r="FK10" t="n">
-        <v>-0.01400474004250794</v>
+        <v>-0.001661299482522363</v>
       </c>
       <c r="FL10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.002676069153934686</v>
+        <v>0.05916860197353268</v>
       </c>
       <c r="FR10" t="n">
         <v>-0</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.06584445349652913</v>
+        <v>0.2004139131456817</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.03211288872499326</v>
+        <v>-0.04762021684997371</v>
       </c>
       <c r="FU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW10" t="n">
         <v>0</v>
@@ -6091,39 +6091,39 @@
         <v>0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>-0.02212208209372212</v>
+        <v>-0.04413449740909142</v>
       </c>
       <c r="GA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB10" t="n">
-        <v>-0.03563408003848977</v>
+        <v>0.1110491267528741</v>
       </c>
       <c r="GC10" t="n">
         <v>0</v>
       </c>
       <c r="GD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE10" t="n">
         <v>-0</v>
       </c>
       <c r="GF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B11" t="n">
-        <v>0.1589610711727572</v>
+        <v>0.2857746919583649</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -6132,10 +6132,10 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.04337964506746834</v>
+        <v>0.03537007003892471</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.10106543879525</v>
+        <v>-0.2590523462962723</v>
       </c>
       <c r="G11" t="n">
         <v>-0</v>
@@ -6144,13 +6144,13 @@
         <v>-0</v>
       </c>
       <c r="I11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1227449045020368</v>
+        <v>0.3236260504814116</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -6159,25 +6159,25 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.01494532506676126</v>
+        <v>-0.08046343143976779</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.05593671828055311</v>
+        <v>-0.207119844763047</v>
       </c>
       <c r="P11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.02863058078650222</v>
+        <v>0.09855191790272509</v>
       </c>
       <c r="U11" t="n">
         <v>-0</v>
@@ -6186,37 +6186,37 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.02229832001961994</v>
+        <v>-0.05429537937613115</v>
       </c>
       <c r="X11" t="n">
-        <v>0.0009944783973878963</v>
+        <v>-0.071265480382568</v>
       </c>
       <c r="Y11" t="n">
         <v>-0</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB11" t="n">
         <v>-0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.0003256268392576414</v>
+        <v>-0.06771747375362412</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.0005517397164854005</v>
+        <v>-0.19185046540687</v>
       </c>
       <c r="AG11" t="n">
-        <v>-0.008504614147312782</v>
+        <v>0.07939889513096077</v>
       </c>
       <c r="AH11" t="n">
         <v>0</v>
@@ -6231,22 +6231,22 @@
         <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.02538074766034841</v>
+        <v>0.1261075475215516</v>
       </c>
       <c r="AM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>-0.008424205901947788</v>
+        <v>-0.03590321270631883</v>
       </c>
       <c r="AP11" t="n">
-        <v>-0.0502531428929397</v>
+        <v>-0.08781443702498574</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR11" t="n">
         <v>-0</v>
@@ -6255,37 +6255,37 @@
         <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.1463275473736579</v>
+        <v>0.536682793244264</v>
       </c>
       <c r="AV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW11" t="n">
         <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>-0.03509795254325043</v>
+        <v>-0.2479381628747725</v>
       </c>
       <c r="AY11" t="n">
-        <v>-0.109345915823353</v>
+        <v>-0.3030646692191742</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.04932863652300052</v>
+        <v>-0.1032356865571286</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
@@ -6294,10 +6294,10 @@
         <v>0</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.04623260542257231</v>
+        <v>0.02523571446271596</v>
       </c>
       <c r="BH11" t="n">
-        <v>-0.04530551014053272</v>
+        <v>-0.08249852919421692</v>
       </c>
       <c r="BI11" t="n">
         <v>-0</v>
@@ -6306,13 +6306,13 @@
         <v>-0</v>
       </c>
       <c r="BK11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.04281810092315083</v>
+        <v>0.09271060381261344</v>
       </c>
       <c r="BN11" t="n">
         <v>-0</v>
@@ -6321,79 +6321,79 @@
         <v>-0</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.02105778762007339</v>
+        <v>0.05598051741071496</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.004317474875009573</v>
+        <v>0.06529185197638886</v>
       </c>
       <c r="BR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS11" t="n">
         <v>0</v>
       </c>
       <c r="BT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU11" t="n">
         <v>-0</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.08404362072520531</v>
+        <v>0.2966657176568378</v>
       </c>
       <c r="BW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX11" t="n">
         <v>0</v>
       </c>
       <c r="BY11" t="n">
-        <v>-0.024025163353162</v>
+        <v>-0.06752403124959275</v>
       </c>
       <c r="BZ11" t="n">
-        <v>-0.03217315708767531</v>
+        <v>-0.1670550283776666</v>
       </c>
       <c r="CA11" t="n">
         <v>-0</v>
       </c>
       <c r="CB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC11" t="n">
         <v>-0</v>
       </c>
       <c r="CD11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE11" t="n">
-        <v>-0.04130357840418181</v>
+        <v>-0.1482602087757987</v>
       </c>
       <c r="CF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG11" t="n">
         <v>-0</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.002236600239076929</v>
+        <v>0.03577410811814859</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.03427002024254591</v>
+        <v>0.09379327247709286</v>
       </c>
       <c r="CJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK11" t="n">
         <v>0</v>
       </c>
       <c r="CL11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM11" t="n">
         <v>0</v>
       </c>
       <c r="CN11" t="n">
-        <v>5.835430320860319e-05</v>
+        <v>-0.06479243335494052</v>
       </c>
       <c r="CO11" t="n">
         <v>-0</v>
@@ -6402,37 +6402,37 @@
         <v>-0</v>
       </c>
       <c r="CQ11" t="n">
-        <v>0.0005470976653379152</v>
+        <v>0.07209929022827558</v>
       </c>
       <c r="CR11" t="n">
-        <v>-0.008606977068776637</v>
+        <v>-0.003504962134377902</v>
       </c>
       <c r="CS11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV11" t="n">
         <v>-0</v>
       </c>
       <c r="CW11" t="n">
-        <v>-0.03680334579194405</v>
+        <v>-0.1408385134544604</v>
       </c>
       <c r="CX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY11" t="n">
         <v>0</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.006678294474540209</v>
+        <v>0.01682759595277486</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.0378188200655074</v>
+        <v>0.1273312971613949</v>
       </c>
       <c r="DB11" t="n">
         <v>0</v>
@@ -6441,25 +6441,25 @@
         <v>-0</v>
       </c>
       <c r="DD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE11" t="n">
         <v>0</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.005967600968891288</v>
+        <v>0.02225370653475057</v>
       </c>
       <c r="DG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.05092798024129717</v>
+        <v>-0.02281476586838516</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.00205764002187583</v>
+        <v>0.04553104920106683</v>
       </c>
       <c r="DK11" t="n">
         <v>0</v>
@@ -6468,13 +6468,13 @@
         <v>0</v>
       </c>
       <c r="DM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN11" t="n">
         <v>-0</v>
       </c>
       <c r="DO11" t="n">
-        <v>-0.01912797001000105</v>
+        <v>-0.1284334160586892</v>
       </c>
       <c r="DP11" t="n">
         <v>0</v>
@@ -6483,25 +6483,25 @@
         <v>0</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.01515440308682065</v>
+        <v>0.02206513787728312</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.009579668336211303</v>
+        <v>0.1516287018265908</v>
       </c>
       <c r="DT11" t="n">
         <v>-0</v>
       </c>
       <c r="DU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV11" t="n">
         <v>0</v>
       </c>
       <c r="DW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX11" t="n">
-        <v>-0.0468107666023125</v>
+        <v>-0.08591236653437558</v>
       </c>
       <c r="DY11" t="n">
         <v>-0</v>
@@ -6510,10 +6510,10 @@
         <v>-0</v>
       </c>
       <c r="EA11" t="n">
-        <v>0.02921393859205576</v>
+        <v>0.09581917862911232</v>
       </c>
       <c r="EB11" t="n">
-        <v>0.01431956995744334</v>
+        <v>0.04027508529279056</v>
       </c>
       <c r="EC11" t="n">
         <v>0</v>
@@ -6522,25 +6522,25 @@
         <v>0</v>
       </c>
       <c r="EE11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF11" t="n">
         <v>0</v>
       </c>
       <c r="EG11" t="n">
-        <v>-0.03381188172023993</v>
+        <v>-0.03079756122882678</v>
       </c>
       <c r="EH11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI11" t="n">
         <v>-0</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.01332405059405311</v>
+        <v>-0.03917122253372658</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.03384596103336049</v>
+        <v>0.01229790601816523</v>
       </c>
       <c r="EL11" t="n">
         <v>-0</v>
@@ -6549,13 +6549,13 @@
         <v>-0</v>
       </c>
       <c r="EN11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO11" t="n">
         <v>0</v>
       </c>
       <c r="EP11" t="n">
-        <v>-0.03358558061923612</v>
+        <v>-0.03997354097047578</v>
       </c>
       <c r="EQ11" t="n">
         <v>-0</v>
@@ -6564,13 +6564,13 @@
         <v>-0</v>
       </c>
       <c r="ES11" t="n">
-        <v>-0.006699547886820608</v>
+        <v>-0.1123377051953602</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.004051194981766691</v>
+        <v>0.0110379251465177</v>
       </c>
       <c r="EU11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV11" t="n">
         <v>0</v>
@@ -6582,7 +6582,7 @@
         <v>0</v>
       </c>
       <c r="EY11" t="n">
-        <v>-0.03691880530666464</v>
+        <v>-0.1624301658955563</v>
       </c>
       <c r="EZ11" t="n">
         <v>-0</v>
@@ -6591,25 +6591,25 @@
         <v>-0</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.007592433114835911</v>
+        <v>0.01077013684796831</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.03584873379244093</v>
+        <v>0.1167006839372136</v>
       </c>
       <c r="FD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE11" t="n">
         <v>0</v>
       </c>
       <c r="FF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG11" t="n">
         <v>0</v>
       </c>
       <c r="FH11" t="n">
-        <v>-0.02113800646607456</v>
+        <v>0.09835018060599673</v>
       </c>
       <c r="FI11" t="n">
         <v>0</v>
@@ -6618,25 +6618,25 @@
         <v>-0</v>
       </c>
       <c r="FK11" t="n">
-        <v>0.01264562921169815</v>
+        <v>-0.03603830282378974</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.03154009075545897</v>
+        <v>0.1380126935321841</v>
       </c>
       <c r="FM11" t="n">
         <v>0</v>
       </c>
       <c r="FN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO11" t="n">
         <v>0</v>
       </c>
       <c r="FP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ11" t="n">
-        <v>-0.001738165228662885</v>
+        <v>0.02396480015362012</v>
       </c>
       <c r="FR11" t="n">
         <v>-0</v>
@@ -6645,37 +6645,37 @@
         <v>-0</v>
       </c>
       <c r="FT11" t="n">
-        <v>-0.02377997533538515</v>
+        <v>-0.05132523783995464</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.02189201655433314</v>
+        <v>-0.02222808092623349</v>
       </c>
       <c r="FV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ11" t="n">
-        <v>-0.005932175969692238</v>
+        <v>-0.03119115905110057</v>
       </c>
       <c r="GA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB11" t="n">
         <v>-0</v>
       </c>
       <c r="GC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD11" t="n">
-        <v>-0.01806336878785947</v>
+        <v>0.14614525878096</v>
       </c>
       <c r="GE11" t="n">
         <v>-0</v>
@@ -6692,46 +6692,46 @@
         <v>0</v>
       </c>
       <c r="B12" t="n">
-        <v>0.2650050552336102</v>
+        <v>0.249027327547678</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.08540261505905275</v>
+        <v>-0.1039970860381959</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.06975935624334557</v>
+        <v>0.005102570623100672</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.02848423300111132</v>
+        <v>-0.1116850877672301</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H12" t="n">
         <v>-0</v>
       </c>
       <c r="I12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2005425909663803</v>
+        <v>0.2992648488818383</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.0469943466558634</v>
+        <v>-0.09888741878714856</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.04950597859014896</v>
+        <v>-0.07156062136863897</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.02572641147043984</v>
+        <v>-0.07684771733471335</v>
       </c>
       <c r="P12" t="n">
         <v>-0</v>
@@ -6746,133 +6746,133 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.06693374759666799</v>
+        <v>0.1042140587440149</v>
       </c>
       <c r="U12" t="n">
         <v>-0</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.01951193003928579</v>
+        <v>-0.07546360958350587</v>
       </c>
       <c r="W12" t="n">
-        <v>0.0323346273786867</v>
+        <v>-0.09181681117021052</v>
       </c>
       <c r="X12" t="n">
-        <v>0.009331752982247294</v>
+        <v>-0.05424444718777578</v>
       </c>
       <c r="Y12" t="n">
         <v>-0</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.05170185397648627</v>
+        <v>-0.05733282575330979</v>
       </c>
       <c r="AD12" t="n">
         <v>-0</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.01795248072868565</v>
+        <v>-0.1375405768613344</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.007370823556753229</v>
+        <v>-0.02843048848614434</v>
       </c>
       <c r="AG12" t="n">
-        <v>-0.01553611506841176</v>
+        <v>0.05376093495995564</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.01749806933138082</v>
+        <v>0.07620863324794441</v>
       </c>
       <c r="AM12" t="n">
         <v>-0</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0.05718022179325975</v>
+        <v>-0.07211119139797018</v>
       </c>
       <c r="AO12" t="n">
-        <v>-0.05612006660120532</v>
+        <v>0.02997404418316774</v>
       </c>
       <c r="AP12" t="n">
-        <v>-0.03241313368255059</v>
+        <v>-0.03724727579007161</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT12" t="n">
         <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.283709686611043</v>
+        <v>0.3603495274571381</v>
       </c>
       <c r="AV12" t="n">
         <v>-0</v>
       </c>
       <c r="AW12" t="n">
-        <v>-0.03799887563040592</v>
+        <v>-0.1528886722530149</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.03156966548561439</v>
+        <v>-0.2018129319214596</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.03179248766445465</v>
+        <v>-0.166437506254554</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
         <v>-0</v>
       </c>
       <c r="BC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.03857323132062866</v>
+        <v>-0.0415745301318473</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>-0.06708321841754265</v>
+        <v>-0.07021492633720067</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.1089795276012803</v>
+        <v>0.005112754921982095</v>
       </c>
       <c r="BH12" t="n">
-        <v>-0.04732587658507667</v>
+        <v>-0.09785357523193189</v>
       </c>
       <c r="BI12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK12" t="n">
         <v>0</v>
@@ -6881,52 +6881,52 @@
         <v>-0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.05716311196925</v>
+        <v>0.03624617049247352</v>
       </c>
       <c r="BN12" t="n">
         <v>-0</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.05144928529924453</v>
+        <v>0.07958018939536891</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.0969430017859292</v>
+        <v>0.01349651784040254</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0.03554574642186482</v>
+        <v>0.0104093269296282</v>
       </c>
       <c r="BR12" t="n">
         <v>0</v>
       </c>
       <c r="BS12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU12" t="n">
         <v>0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.1270514975099279</v>
+        <v>0.1950483753457889</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX12" t="n">
-        <v>-0.0008018622796258022</v>
+        <v>-0.09039625522185822</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.01434587305899816</v>
+        <v>-0.06764743250590358</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0.01244655151281326</v>
+        <v>-0.1303099297385667</v>
       </c>
       <c r="CA12" t="n">
         <v>-0</v>
       </c>
       <c r="CB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC12" t="n">
         <v>-0</v>
@@ -6935,22 +6935,22 @@
         <v>0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.06739645866687233</v>
+        <v>-0.08965416294631859</v>
       </c>
       <c r="CF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.01058010982736738</v>
+        <v>0.09017318740581234</v>
       </c>
       <c r="CH12" t="n">
-        <v>-0.000167696443055077</v>
+        <v>-0.003744394432621063</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.02326035387194274</v>
+        <v>0.04262726363915661</v>
       </c>
       <c r="CJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK12" t="n">
         <v>0</v>
@@ -6962,49 +6962,49 @@
         <v>0</v>
       </c>
       <c r="CN12" t="n">
-        <v>-0.0004563207409788877</v>
+        <v>-0.02033285749113068</v>
       </c>
       <c r="CO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP12" t="n">
-        <v>-0.02145531359072898</v>
+        <v>0.08425727299422703</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.02742448701147641</v>
+        <v>0.04645953571720601</v>
       </c>
       <c r="CR12" t="n">
-        <v>-0.008938100021586157</v>
+        <v>0.01536426539140878</v>
       </c>
       <c r="CS12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.0548676370488267</v>
+        <v>-0.097334941253773</v>
       </c>
       <c r="CX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.03137085279995845</v>
+        <v>0.1100057958453151</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.003399438728241294</v>
+        <v>0.002864686545440955</v>
       </c>
       <c r="DA12" t="n">
-        <v>0.02270225672176187</v>
+        <v>0.07032382080882771</v>
       </c>
       <c r="DB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC12" t="n">
         <v>-0</v>
@@ -7016,19 +7016,19 @@
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>-0.02150088328165945</v>
+        <v>-0.05420950208610163</v>
       </c>
       <c r="DG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.04760994177240586</v>
+        <v>0.023444112619843</v>
       </c>
       <c r="DI12" t="n">
-        <v>-0.003956014878707961</v>
+        <v>0.009200420788710457</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0.01211590241616265</v>
+        <v>0.02488552882447583</v>
       </c>
       <c r="DK12" t="n">
         <v>-0</v>
@@ -7037,31 +7037,31 @@
         <v>0</v>
       </c>
       <c r="DM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.009691239470002538</v>
+        <v>0.0006608814544339273</v>
       </c>
       <c r="DP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.03921305234909025</v>
+        <v>0.01599843077978104</v>
       </c>
       <c r="DR12" t="n">
-        <v>-0.01792211719686711</v>
+        <v>-0.1030395015917234</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.02249507212371893</v>
+        <v>-0.008142391488326442</v>
       </c>
       <c r="DT12" t="n">
         <v>-0</v>
       </c>
       <c r="DU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV12" t="n">
         <v>0</v>
@@ -7070,76 +7070,76 @@
         <v>-0</v>
       </c>
       <c r="DX12" t="n">
-        <v>-0.03283059838521874</v>
+        <v>-0.03421514678468975</v>
       </c>
       <c r="DY12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ12" t="n">
-        <v>-0.01638419330862931</v>
+        <v>0.07825713762211674</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.008181814645566087</v>
+        <v>0.005783623328588454</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.03278814517648578</v>
+        <v>-0.03475952361142329</v>
       </c>
       <c r="EC12" t="n">
         <v>0</v>
       </c>
       <c r="ED12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF12" t="n">
         <v>0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.07838729814648575</v>
+        <v>-0.0806831319280388</v>
       </c>
       <c r="EH12" t="n">
         <v>-0</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.03280448861266706</v>
+        <v>0.09199625827097606</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.05359052649747519</v>
+        <v>0.0193243416531384</v>
       </c>
       <c r="EK12" t="n">
-        <v>0.01666918280884291</v>
+        <v>-0.036272286935615</v>
       </c>
       <c r="EL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM12" t="n">
         <v>-0</v>
       </c>
       <c r="EN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO12" t="n">
         <v>0</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.04977002161745193</v>
+        <v>-0.03450502888511527</v>
       </c>
       <c r="EQ12" t="n">
         <v>-0</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.0247012017739537</v>
+        <v>0.0609551997732563</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.01955589592977269</v>
+        <v>0.01752867232073513</v>
       </c>
       <c r="ET12" t="n">
-        <v>0.0411708205520129</v>
+        <v>0.07581684700087714</v>
       </c>
       <c r="EU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV12" t="n">
         <v>0</v>
@@ -7151,19 +7151,19 @@
         <v>0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.0545583148656341</v>
+        <v>-0.1014948293199905</v>
       </c>
       <c r="EZ12" t="n">
         <v>-0</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.01357296279110911</v>
+        <v>0.1283210047609431</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.008851729330875975</v>
+        <v>-0.01515149501166281</v>
       </c>
       <c r="FC12" t="n">
-        <v>0.02804907976287273</v>
+        <v>0.05657620585043636</v>
       </c>
       <c r="FD12" t="n">
         <v>0</v>
@@ -7175,79 +7175,79 @@
         <v>0</v>
       </c>
       <c r="FG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH12" t="n">
-        <v>-0.02425699566946161</v>
+        <v>0.09704186372855188</v>
       </c>
       <c r="FI12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.03839659592325681</v>
+        <v>0.08967153372796453</v>
       </c>
       <c r="FK12" t="n">
-        <v>0.001711482106203641</v>
+        <v>0.007460468439977981</v>
       </c>
       <c r="FL12" t="n">
-        <v>-0.01543114945773326</v>
+        <v>0.144217944672616</v>
       </c>
       <c r="FM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO12" t="n">
         <v>0</v>
       </c>
       <c r="FP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>-0.0038207607570778</v>
+        <v>0.01292869213476163</v>
       </c>
       <c r="FR12" t="n">
         <v>0</v>
       </c>
       <c r="FS12" t="n">
-        <v>0.0171613403516136</v>
+        <v>0.1511968485040224</v>
       </c>
       <c r="FT12" t="n">
-        <v>-0.02240357659577574</v>
+        <v>-0.04224949618086624</v>
       </c>
       <c r="FU12" t="n">
-        <v>0.021148376001634</v>
+        <v>0.004225501040959629</v>
       </c>
       <c r="FV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX12" t="n">
         <v>0</v>
       </c>
       <c r="FY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.01759752878040514</v>
+        <v>-0.02898381804717588</v>
       </c>
       <c r="GA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB12" t="n">
-        <v>-0.05007373062138434</v>
+        <v>0.03407079336371571</v>
       </c>
       <c r="GC12" t="n">
         <v>-0</v>
       </c>
       <c r="GD12" t="n">
-        <v>-0.02551342436708259</v>
+        <v>0.07627047447481823</v>
       </c>
       <c r="GE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF12" t="n">
         <v>0</v>
@@ -7261,43 +7261,43 @@
         <v>0</v>
       </c>
       <c r="B13" t="n">
-        <v>0.2387077326513741</v>
+        <v>0.2215322855406511</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.06797784265224502</v>
+        <v>-0.08079226242696226</v>
       </c>
       <c r="E13" t="n">
-        <v>0.001104353515527399</v>
+        <v>-0.02016813462993244</v>
       </c>
       <c r="F13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1755553893213557</v>
+        <v>0.2633574869799849</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.06562201846455426</v>
+        <v>-0.0892453523440256</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.01033087717111966</v>
+        <v>-0.05682904430409131</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -7315,19 +7315,19 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.06227265993710771</v>
+        <v>0.05709312059146299</v>
       </c>
       <c r="U13" t="n">
         <v>-0</v>
       </c>
       <c r="V13" t="n">
-        <v>0.01248100295046824</v>
+        <v>-0.02100990021384219</v>
       </c>
       <c r="W13" t="n">
-        <v>0.07309294609813236</v>
+        <v>-0.0298876619281884</v>
       </c>
       <c r="X13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
@@ -7336,112 +7336,112 @@
         <v>-0</v>
       </c>
       <c r="AA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.06290120153465241</v>
+        <v>-0.0121731531045291</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0.01986259900349703</v>
+        <v>-0.09044999853162897</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.01468156550347631</v>
+        <v>-0.01320952748630769</v>
       </c>
       <c r="AG13" t="n">
         <v>-0</v>
       </c>
       <c r="AH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>-0.01928408265896196</v>
+        <v>0.06948722428070421</v>
       </c>
       <c r="AM13" t="n">
         <v>-0</v>
       </c>
       <c r="AN13" t="n">
-        <v>-0.06023233303281686</v>
+        <v>-0.05501460077428859</v>
       </c>
       <c r="AO13" t="n">
-        <v>-0.04753725293071204</v>
+        <v>0.07577286768521159</v>
       </c>
       <c r="AP13" t="n">
         <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT13" t="n">
         <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.2358114980705751</v>
+        <v>0.209726271567324</v>
       </c>
       <c r="AV13" t="n">
         <v>-0</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.0251648680282537</v>
+        <v>-0.05016551727715616</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.1222662474380745</v>
+        <v>-0.1217762517991149</v>
       </c>
       <c r="AY13" t="n">
         <v>-0</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
         <v>-0</v>
       </c>
       <c r="BC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.03701665347282697</v>
+        <v>-0.0002954124804574009</v>
       </c>
       <c r="BE13" t="n">
         <v>0</v>
       </c>
       <c r="BF13" t="n">
-        <v>-0.1045919969614737</v>
+        <v>-0.03481541974007678</v>
       </c>
       <c r="BG13" t="n">
-        <v>-0.06599275087908038</v>
+        <v>-0.03824798642571543</v>
       </c>
       <c r="BH13" t="n">
         <v>0</v>
       </c>
       <c r="BI13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK13" t="n">
         <v>0</v>
@@ -7450,16 +7450,16 @@
         <v>-0</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.04892852460553179</v>
+        <v>-0.007816482788425914</v>
       </c>
       <c r="BN13" t="n">
         <v>-0</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.03216264329681798</v>
+        <v>0.02128912590302387</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.1603512934418344</v>
+        <v>0.05874445731005184</v>
       </c>
       <c r="BQ13" t="n">
         <v>-0</v>
@@ -7471,52 +7471,52 @@
         <v>-0</v>
       </c>
       <c r="BT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU13" t="n">
         <v>0</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.100258298234984</v>
+        <v>0.1477717059555307</v>
       </c>
       <c r="BW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.03564841989720731</v>
+        <v>-0.04455999138645179</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.0829458903503518</v>
+        <v>-0.02206597306520466</v>
       </c>
       <c r="BZ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA13" t="n">
         <v>-0</v>
       </c>
       <c r="CB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE13" t="n">
-        <v>-0.06375369148944911</v>
+        <v>-0.08643282900751541</v>
       </c>
       <c r="CF13" t="n">
         <v>-0</v>
       </c>
       <c r="CG13" t="n">
-        <v>-0.002057769314283808</v>
+        <v>0.06991048155246572</v>
       </c>
       <c r="CH13" t="n">
-        <v>-0.01211326570539124</v>
+        <v>0.0007775842720287341</v>
       </c>
       <c r="CI13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ13" t="n">
         <v>0</v>
@@ -7531,22 +7531,22 @@
         <v>0</v>
       </c>
       <c r="CN13" t="n">
-        <v>-0.007045938190649382</v>
+        <v>-0.03656406692152463</v>
       </c>
       <c r="CO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP13" t="n">
-        <v>-0.04091356998396182</v>
+        <v>0.09783575108328708</v>
       </c>
       <c r="CQ13" t="n">
-        <v>-0.04152978998435907</v>
+        <v>0.0178055101731727</v>
       </c>
       <c r="CR13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT13" t="n">
         <v>0</v>
@@ -7558,16 +7558,16 @@
         <v>0</v>
       </c>
       <c r="CW13" t="n">
-        <v>-0.04897435773996345</v>
+        <v>-0.08397317352705837</v>
       </c>
       <c r="CX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.01407872682882558</v>
+        <v>0.08032853063722784</v>
       </c>
       <c r="CZ13" t="n">
-        <v>-0.01055997007038905</v>
+        <v>0.005926514242300427</v>
       </c>
       <c r="DA13" t="n">
         <v>-0</v>
@@ -7585,16 +7585,16 @@
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>-0.03329815417478197</v>
+        <v>-0.04520296707651449</v>
       </c>
       <c r="DG13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.01542770324616192</v>
+        <v>0.017640048201015</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.01639791657613373</v>
+        <v>-0.04859064878530735</v>
       </c>
       <c r="DJ13" t="n">
         <v>-0</v>
@@ -7606,76 +7606,76 @@
         <v>0</v>
       </c>
       <c r="DM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>-0.03008037215508554</v>
+        <v>-0.03716930061347866</v>
       </c>
       <c r="DP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0.05652770668976206</v>
+        <v>-0.07453626424573065</v>
       </c>
       <c r="DR13" t="n">
-        <v>-0.02108192290297939</v>
+        <v>-0.04941527942768822</v>
       </c>
       <c r="DS13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT13" t="n">
         <v>-0</v>
       </c>
       <c r="DU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW13" t="n">
         <v>-0</v>
       </c>
       <c r="DX13" t="n">
-        <v>-0.04520444708774131</v>
+        <v>-0.02180477969716717</v>
       </c>
       <c r="DY13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ13" t="n">
-        <v>-0.004664726215604025</v>
+        <v>0.03619524976552568</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.01267861156450676</v>
+        <v>-0.02380579988771007</v>
       </c>
       <c r="EB13" t="n">
         <v>0</v>
       </c>
       <c r="EC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG13" t="n">
-        <v>-0.06565789102703237</v>
+        <v>-0.06136348149235122</v>
       </c>
       <c r="EH13" t="n">
         <v>-0</v>
       </c>
       <c r="EI13" t="n">
-        <v>0.01726239131675898</v>
+        <v>0.04812467311105083</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.04920354457150818</v>
+        <v>0.03369574305309238</v>
       </c>
       <c r="EK13" t="n">
         <v>0</v>
@@ -7684,55 +7684,55 @@
         <v>-0</v>
       </c>
       <c r="EM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN13" t="n">
         <v>-0</v>
       </c>
       <c r="EO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP13" t="n">
-        <v>-0.04520889281590022</v>
+        <v>-0.02257998965145745</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.01966675362094232</v>
+        <v>-0.001199203358449382</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.03223192967828856</v>
+        <v>-0.00859310801383986</v>
       </c>
       <c r="ET13" t="n">
         <v>0</v>
       </c>
       <c r="EU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV13" t="n">
         <v>0</v>
       </c>
       <c r="EW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY13" t="n">
-        <v>-0.05065950007802948</v>
+        <v>-0.09143585770166456</v>
       </c>
       <c r="EZ13" t="n">
         <v>-0</v>
       </c>
       <c r="FA13" t="n">
-        <v>-0.009093770341052227</v>
+        <v>0.09278531423937351</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.005435958414426116</v>
+        <v>-0.01538801888340146</v>
       </c>
       <c r="FC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD13" t="n">
         <v>0</v>
@@ -7747,16 +7747,16 @@
         <v>0</v>
       </c>
       <c r="FH13" t="n">
-        <v>-0.03770416571436889</v>
+        <v>0.08445161908174242</v>
       </c>
       <c r="FI13" t="n">
         <v>-0</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0.0009175467341158154</v>
+        <v>0.06760642479062147</v>
       </c>
       <c r="FK13" t="n">
-        <v>0.03981059378440965</v>
+        <v>-0.01357754812205016</v>
       </c>
       <c r="FL13" t="n">
         <v>-0</v>
@@ -7768,69 +7768,69 @@
         <v>-0</v>
       </c>
       <c r="FO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>-0.00144458590414132</v>
+        <v>0.00121688941597181</v>
       </c>
       <c r="FR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS13" t="n">
-        <v>-0.001284400071262812</v>
+        <v>0.0929289061692383</v>
       </c>
       <c r="FT13" t="n">
-        <v>-0.006469988742281124</v>
+        <v>-0.01806901786159286</v>
       </c>
       <c r="FU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV13" t="n">
         <v>0</v>
       </c>
       <c r="FW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX13" t="n">
         <v>0</v>
       </c>
       <c r="FY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.01972838523788178</v>
+        <v>-0.06488978468003571</v>
       </c>
       <c r="GA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB13" t="n">
-        <v>-0.09186509288272342</v>
+        <v>0.02264964297637794</v>
       </c>
       <c r="GC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD13" t="n">
         <v>-0</v>
       </c>
       <c r="GE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B14" t="n">
-        <v>0.2878147212338333</v>
+        <v>0.3592665774559661</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -7839,10 +7839,10 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.06903426678540173</v>
+        <v>0.0124110029667905</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.1861605570832192</v>
+        <v>-0.3185349832123135</v>
       </c>
       <c r="G14" t="n">
         <v>-0</v>
@@ -7851,13 +7851,13 @@
         <v>-0</v>
       </c>
       <c r="I14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K14" t="n">
-        <v>0.2577700144135838</v>
+        <v>0.4887661062873814</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -7866,25 +7866,25 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.01676982683713597</v>
+        <v>-0.06469976493982263</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1812069610603313</v>
+        <v>-0.408413885587264</v>
       </c>
       <c r="P14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T14" t="n">
-        <v>0.02997240260031061</v>
+        <v>0.1348631657901264</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -7893,67 +7893,67 @@
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.01091782248889533</v>
+        <v>-0.08997640117938424</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.01066161805841402</v>
+        <v>-0.0684747771039094</v>
       </c>
       <c r="Y14" t="n">
         <v>-0</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB14" t="n">
         <v>-0</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.01514748725954933</v>
+        <v>-0.02099978615454538</v>
       </c>
       <c r="AD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.03799535978859657</v>
+        <v>-0.2762934213857937</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.004067049017134807</v>
+        <v>0.09734500500817471</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI14" t="n">
         <v>-0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.04255185539692295</v>
+        <v>0.1238131272451377</v>
       </c>
       <c r="AM14" t="n">
         <v>-0</v>
       </c>
       <c r="AN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
-        <v>-0.004216380830539836</v>
+        <v>-0.05949332035183696</v>
       </c>
       <c r="AP14" t="n">
-        <v>-0.0639193299035308</v>
+        <v>-0.08840890567862766</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR14" t="n">
         <v>-0</v>
@@ -7962,37 +7962,37 @@
         <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.2284602772073094</v>
+        <v>0.6463937434838852</v>
       </c>
       <c r="AV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX14" t="n">
-        <v>-0.01842010448539014</v>
+        <v>-0.2885792206392588</v>
       </c>
       <c r="AY14" t="n">
-        <v>-0.07901639720775332</v>
+        <v>-0.1997911008837412</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.05833942486599913</v>
+        <v>-0.1126946781311991</v>
       </c>
       <c r="BE14" t="n">
         <v>0</v>
@@ -8001,64 +8001,64 @@
         <v>0</v>
       </c>
       <c r="BG14" t="n">
-        <v>-0.06472983427533363</v>
+        <v>-0.02566080516115521</v>
       </c>
       <c r="BH14" t="n">
-        <v>-0.08219059373657751</v>
+        <v>-0.03750661578764619</v>
       </c>
       <c r="BI14" t="n">
         <v>0</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.04620553626372256</v>
+        <v>0.1267599079000587</v>
       </c>
       <c r="BN14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO14" t="n">
         <v>-0</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.01785785903410116</v>
+        <v>0.07541834802918621</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0.005465321145655151</v>
+        <v>0.04127890339293192</v>
       </c>
       <c r="BR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS14" t="n">
         <v>-0</v>
       </c>
       <c r="BT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.114615607703585</v>
+        <v>0.3700263990427802</v>
       </c>
       <c r="BW14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX14" t="n">
         <v>0</v>
       </c>
       <c r="BY14" t="n">
-        <v>-0.02948840970321008</v>
+        <v>-0.03550810160760057</v>
       </c>
       <c r="BZ14" t="n">
-        <v>-0.04878079628020656</v>
+        <v>-0.182342771419829</v>
       </c>
       <c r="CA14" t="n">
         <v>-0</v>
@@ -8067,28 +8067,28 @@
         <v>-0</v>
       </c>
       <c r="CC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD14" t="n">
         <v>0</v>
       </c>
       <c r="CE14" t="n">
-        <v>-0.0648703088395393</v>
+        <v>-0.1485052524197779</v>
       </c>
       <c r="CF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG14" t="n">
         <v>-0</v>
       </c>
       <c r="CH14" t="n">
-        <v>-0.007721770691504358</v>
+        <v>0.03170414698786368</v>
       </c>
       <c r="CI14" t="n">
-        <v>0.03872908045458783</v>
+        <v>0.10798569496285</v>
       </c>
       <c r="CJ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK14" t="n">
         <v>0</v>
@@ -8100,73 +8100,73 @@
         <v>0</v>
       </c>
       <c r="CN14" t="n">
-        <v>0.003525744495956261</v>
+        <v>-0.1446464043346002</v>
       </c>
       <c r="CO14" t="n">
         <v>-0</v>
       </c>
       <c r="CP14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ14" t="n">
-        <v>-0.01611087152957932</v>
+        <v>0.1146393546140499</v>
       </c>
       <c r="CR14" t="n">
-        <v>-0.05644652086419788</v>
+        <v>0.02857141539470635</v>
       </c>
       <c r="CS14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV14" t="n">
         <v>-0</v>
       </c>
       <c r="CW14" t="n">
-        <v>-0.05921382478101779</v>
+        <v>-0.1404595684646018</v>
       </c>
       <c r="CX14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY14" t="n">
         <v>0</v>
       </c>
       <c r="CZ14" t="n">
-        <v>-0.007590635846527114</v>
+        <v>0.01524570695447108</v>
       </c>
       <c r="DA14" t="n">
-        <v>0.0401456629436726</v>
+        <v>0.1398991042049428</v>
       </c>
       <c r="DB14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC14" t="n">
         <v>-0</v>
       </c>
       <c r="DD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE14" t="n">
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>-0.03323712693232195</v>
+        <v>-0.1112803389875733</v>
       </c>
       <c r="DG14" t="n">
         <v>0</v>
       </c>
       <c r="DH14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.06211845463833868</v>
+        <v>-0.05844885863992825</v>
       </c>
       <c r="DJ14" t="n">
-        <v>0.04859796409482577</v>
+        <v>0.08664942347776897</v>
       </c>
       <c r="DK14" t="n">
         <v>0</v>
@@ -8175,13 +8175,13 @@
         <v>0</v>
       </c>
       <c r="DM14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN14" t="n">
         <v>-0</v>
       </c>
       <c r="DO14" t="n">
-        <v>-0.02722390994583234</v>
+        <v>-0.08910546458876216</v>
       </c>
       <c r="DP14" t="n">
         <v>0</v>
@@ -8190,94 +8190,94 @@
         <v>0</v>
       </c>
       <c r="DR14" t="n">
-        <v>0.02287095351202065</v>
+        <v>-0.0005639195766592671</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.01431597885538048</v>
+        <v>0.1093306977228302</v>
       </c>
       <c r="DT14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW14" t="n">
         <v>-0</v>
       </c>
       <c r="DX14" t="n">
-        <v>-0.05460411774411725</v>
+        <v>-0.06335993665451449</v>
       </c>
       <c r="DY14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.01521494923011018</v>
+        <v>-0.007427109329146578</v>
       </c>
       <c r="EB14" t="n">
-        <v>0.03231451210163941</v>
+        <v>0.0352411578116134</v>
       </c>
       <c r="EC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF14" t="n">
         <v>0</v>
       </c>
       <c r="EG14" t="n">
-        <v>-0.06896587327047683</v>
+        <v>-0.03320885329837635</v>
       </c>
       <c r="EH14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI14" t="n">
         <v>-0</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.02754018855389256</v>
+        <v>-0.02386518241475493</v>
       </c>
       <c r="EK14" t="n">
-        <v>0.0253394665324788</v>
+        <v>0.02759106305415946</v>
       </c>
       <c r="EL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM14" t="n">
         <v>-0</v>
       </c>
       <c r="EN14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO14" t="n">
         <v>0</v>
       </c>
       <c r="EP14" t="n">
-        <v>-0.05035544475187786</v>
+        <v>-0.05758744597421768</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER14" t="n">
         <v>-0</v>
       </c>
       <c r="ES14" t="n">
-        <v>-0.03500058140180162</v>
+        <v>-0.07571519355732911</v>
       </c>
       <c r="ET14" t="n">
-        <v>0.008463769422931347</v>
+        <v>-0.008201805572983724</v>
       </c>
       <c r="EU14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV14" t="n">
         <v>0</v>
@@ -8289,46 +8289,46 @@
         <v>0</v>
       </c>
       <c r="EY14" t="n">
-        <v>-0.05914737327037439</v>
+        <v>-0.1689420317745762</v>
       </c>
       <c r="EZ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA14" t="n">
         <v>-0</v>
       </c>
       <c r="FB14" t="n">
-        <v>-0.001121468935411549</v>
+        <v>-0.006821154732513475</v>
       </c>
       <c r="FC14" t="n">
-        <v>0.03988739638894542</v>
+        <v>0.1216136351736869</v>
       </c>
       <c r="FD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE14" t="n">
         <v>0</v>
       </c>
       <c r="FF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG14" t="n">
         <v>0</v>
       </c>
       <c r="FH14" t="n">
-        <v>-0.03157828800321573</v>
+        <v>0.113972084665418</v>
       </c>
       <c r="FI14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ14" t="n">
         <v>-0</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.007263258386767567</v>
+        <v>-0.06401186692973805</v>
       </c>
       <c r="FL14" t="n">
-        <v>0.03666540696353879</v>
+        <v>0.1740780511956319</v>
       </c>
       <c r="FM14" t="n">
         <v>0</v>
@@ -8340,10 +8340,10 @@
         <v>0</v>
       </c>
       <c r="FP14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ14" t="n">
-        <v>-0.000422044898886936</v>
+        <v>0.009837011797909613</v>
       </c>
       <c r="FR14" t="n">
         <v>-0</v>
@@ -8352,37 +8352,37 @@
         <v>-0</v>
       </c>
       <c r="FT14" t="n">
-        <v>-0.002354695548638968</v>
+        <v>-0.007780681991905951</v>
       </c>
       <c r="FU14" t="n">
-        <v>0.04851509601175726</v>
+        <v>-0.0723317750183132</v>
       </c>
       <c r="FV14" t="n">
         <v>-0</v>
       </c>
       <c r="FW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ14" t="n">
-        <v>0.0005669519955003551</v>
+        <v>-0.02381991724614782</v>
       </c>
       <c r="GA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB14" t="n">
         <v>-0</v>
       </c>
       <c r="GC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD14" t="n">
-        <v>-0.04211418995605395</v>
+        <v>0.1680208705088072</v>
       </c>
       <c r="GE14" t="n">
         <v>-0</v>
@@ -8391,7 +8391,7 @@
         <v>-0</v>
       </c>
       <c r="GG14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -8399,7 +8399,7 @@
         <v>0</v>
       </c>
       <c r="B15" t="n">
-        <v>0.4870340664615532</v>
+        <v>0.3451182324101872</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -8408,16 +8408,16 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.1171038079518017</v>
+        <v>-0.02415007276200525</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4436249964418046</v>
+        <v>-0.1423975481477552</v>
       </c>
       <c r="G15" t="n">
         <v>-0</v>
       </c>
       <c r="H15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -8426,7 +8426,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.4564442769178869</v>
+        <v>0.4556398729406052</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -8435,25 +8435,25 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.05570592675916219</v>
+        <v>-0.1057542333602102</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4518573142021146</v>
+        <v>-0.2037387679502438</v>
       </c>
       <c r="P15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0.03678668043720053</v>
+        <v>0.0994621737550056</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -8462,16 +8462,16 @@
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.08439262822239568</v>
+        <v>-0.1181451646230026</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.01567068857811676</v>
+        <v>-0.01165391202914747</v>
       </c>
       <c r="Y15" t="n">
         <v>-0</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -8480,19 +8480,19 @@
         <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>-0.02363507836424826</v>
+        <v>-0.03181093238320283</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0.01012467495818293</v>
+        <v>-0.2802260515972894</v>
       </c>
       <c r="AG15" t="n">
-        <v>-0.03447034086699631</v>
+        <v>-0.0004806981102348303</v>
       </c>
       <c r="AH15" t="n">
         <v>-0</v>
@@ -8507,7 +8507,7 @@
         <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.08346482370634739</v>
+        <v>0.03391320067782991</v>
       </c>
       <c r="AM15" t="n">
         <v>-0</v>
@@ -8516,10 +8516,10 @@
         <v>0</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.001425139274130004</v>
+        <v>-0.04382687751844315</v>
       </c>
       <c r="AP15" t="n">
-        <v>-0.08288815890890448</v>
+        <v>0.01800998439388342</v>
       </c>
       <c r="AQ15" t="n">
         <v>-0</v>
@@ -8531,10 +8531,10 @@
         <v>0</v>
       </c>
       <c r="AT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.4142823062989933</v>
+        <v>0.490930550772916</v>
       </c>
       <c r="AV15" t="n">
         <v>-0</v>
@@ -8543,16 +8543,16 @@
         <v>0</v>
       </c>
       <c r="AX15" t="n">
-        <v>-0.07056162875261536</v>
+        <v>-0.2412630341333792</v>
       </c>
       <c r="AY15" t="n">
-        <v>-0.2195072107427806</v>
+        <v>-0.1060183635823349</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="n">
         <v>0</v>
@@ -8561,7 +8561,7 @@
         <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.1084983479853896</v>
+        <v>-0.03244371999040717</v>
       </c>
       <c r="BE15" t="n">
         <v>0</v>
@@ -8570,52 +8570,52 @@
         <v>0</v>
       </c>
       <c r="BG15" t="n">
-        <v>-0.1511296373082835</v>
+        <v>-0.01743696709524062</v>
       </c>
       <c r="BH15" t="n">
-        <v>-0.1920463743209763</v>
+        <v>-0.08854328880803962</v>
       </c>
       <c r="BI15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK15" t="n">
         <v>0</v>
       </c>
       <c r="BL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.1430673738132707</v>
+        <v>0.0555858806580355</v>
       </c>
       <c r="BN15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO15" t="n">
         <v>-0</v>
       </c>
       <c r="BP15" t="n">
-        <v>-0.003506804419984493</v>
+        <v>0.08095184223925117</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0.01774829638850664</v>
+        <v>-0.0353695774531211</v>
       </c>
       <c r="BR15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU15" t="n">
         <v>-0</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.2174578064331273</v>
+        <v>0.2645884054932645</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
@@ -8624,10 +8624,10 @@
         <v>0</v>
       </c>
       <c r="BY15" t="n">
-        <v>-0.07027843473932166</v>
+        <v>-0.07607225122038919</v>
       </c>
       <c r="BZ15" t="n">
-        <v>-0.1317131469424722</v>
+        <v>-0.1065766498934343</v>
       </c>
       <c r="CA15" t="n">
         <v>-0</v>
@@ -8642,22 +8642,22 @@
         <v>-0</v>
       </c>
       <c r="CE15" t="n">
-        <v>-0.08493679991571336</v>
+        <v>-0.1128628071677499</v>
       </c>
       <c r="CF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG15" t="n">
         <v>-0</v>
       </c>
       <c r="CH15" t="n">
-        <v>-0.005132296706541574</v>
+        <v>0.02940671068759908</v>
       </c>
       <c r="CI15" t="n">
-        <v>0.107260316561954</v>
+        <v>0.05005876308788209</v>
       </c>
       <c r="CJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK15" t="n">
         <v>0</v>
@@ -8669,100 +8669,100 @@
         <v>0</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.411111576022698e-05</v>
+        <v>-0.1176648399683078</v>
       </c>
       <c r="CO15" t="n">
         <v>-0</v>
       </c>
       <c r="CP15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ15" t="n">
-        <v>0.01656313510158922</v>
+        <v>0.0987659328249483</v>
       </c>
       <c r="CR15" t="n">
-        <v>-0.02173635870421967</v>
+        <v>0.09696302121904032</v>
       </c>
       <c r="CS15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW15" t="n">
-        <v>-0.06794519309467903</v>
+        <v>-0.1132667735478171</v>
       </c>
       <c r="CX15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY15" t="n">
         <v>0</v>
       </c>
       <c r="CZ15" t="n">
-        <v>-0.002517826506811512</v>
+        <v>0.008266387471978583</v>
       </c>
       <c r="DA15" t="n">
-        <v>0.1129463761574095</v>
+        <v>0.07134993351079165</v>
       </c>
       <c r="DB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC15" t="n">
         <v>-0</v>
       </c>
       <c r="DD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE15" t="n">
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>-0.04002326517017469</v>
+        <v>-0.04182103570936625</v>
       </c>
       <c r="DG15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.0444566794875837</v>
+        <v>-0.1773522024170269</v>
       </c>
       <c r="DJ15" t="n">
-        <v>-0.001614683906987056</v>
+        <v>0.05430905562071246</v>
       </c>
       <c r="DK15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM15" t="n">
         <v>0</v>
       </c>
       <c r="DN15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO15" t="n">
-        <v>0.006081052987154392</v>
+        <v>-0.006789881564130029</v>
       </c>
       <c r="DP15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR15" t="n">
-        <v>0.03351720870604942</v>
+        <v>-0.06165173203514228</v>
       </c>
       <c r="DS15" t="n">
-        <v>-0.00651404814989466</v>
+        <v>0.07945600496514979</v>
       </c>
       <c r="DT15" t="n">
         <v>-0</v>
@@ -8771,13 +8771,13 @@
         <v>-0</v>
       </c>
       <c r="DV15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW15" t="n">
         <v>-0</v>
       </c>
       <c r="DX15" t="n">
-        <v>-0.05777594466092893</v>
+        <v>-0.0203989119697206</v>
       </c>
       <c r="DY15" t="n">
         <v>0</v>
@@ -8786,106 +8786,106 @@
         <v>-0</v>
       </c>
       <c r="EA15" t="n">
-        <v>0.01639577769065341</v>
+        <v>-0.0676568575607339</v>
       </c>
       <c r="EB15" t="n">
-        <v>0.05440360332127209</v>
+        <v>0.03633715307927934</v>
       </c>
       <c r="EC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED15" t="n">
         <v>0</v>
       </c>
       <c r="EE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG15" t="n">
-        <v>-0.09693440032671177</v>
+        <v>-0.04598912915854268</v>
       </c>
       <c r="EH15" t="n">
         <v>0</v>
       </c>
       <c r="EI15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.02439302318152298</v>
+        <v>0.02204225341916105</v>
       </c>
       <c r="EK15" t="n">
-        <v>0.1195640580710318</v>
+        <v>-0.009853383573066175</v>
       </c>
       <c r="EL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM15" t="n">
         <v>-0</v>
       </c>
       <c r="EN15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP15" t="n">
-        <v>-0.02990216264525762</v>
+        <v>-0.005227696832770167</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER15" t="n">
         <v>-0</v>
       </c>
       <c r="ES15" t="n">
-        <v>-0.01296633880913288</v>
+        <v>-0.01220162516658875</v>
       </c>
       <c r="ET15" t="n">
-        <v>0.07094629067274934</v>
+        <v>0.1364584260180013</v>
       </c>
       <c r="EU15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV15" t="n">
         <v>0</v>
       </c>
       <c r="EW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY15" t="n">
-        <v>-0.06543195927951648</v>
+        <v>-0.130932432158351</v>
       </c>
       <c r="EZ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA15" t="n">
         <v>-0</v>
       </c>
       <c r="FB15" t="n">
-        <v>0.006229404879093165</v>
+        <v>-0.002061555924192711</v>
       </c>
       <c r="FC15" t="n">
-        <v>0.1024537790435004</v>
+        <v>0.03987951912620769</v>
       </c>
       <c r="FD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG15" t="n">
         <v>0</v>
       </c>
       <c r="FH15" t="n">
-        <v>-0.002535719417640378</v>
+        <v>0.2075057372435904</v>
       </c>
       <c r="FI15" t="n">
         <v>-0</v>
@@ -8894,16 +8894,16 @@
         <v>-0</v>
       </c>
       <c r="FK15" t="n">
-        <v>-0.008508884200727705</v>
+        <v>-0.08888362194263089</v>
       </c>
       <c r="FL15" t="n">
-        <v>0.05172385674770193</v>
+        <v>0.1169911234280748</v>
       </c>
       <c r="FM15" t="n">
         <v>0</v>
       </c>
       <c r="FN15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO15" t="n">
         <v>0</v>
@@ -8912,46 +8912,46 @@
         <v>0</v>
       </c>
       <c r="FQ15" t="n">
-        <v>0.004963051982165477</v>
+        <v>0.01095474566180105</v>
       </c>
       <c r="FR15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS15" t="n">
         <v>-0</v>
       </c>
       <c r="FT15" t="n">
-        <v>-0.008810654514323803</v>
+        <v>-0.02433236845990461</v>
       </c>
       <c r="FU15" t="n">
-        <v>0.03438754936987051</v>
+        <v>-0.04959525460895942</v>
       </c>
       <c r="FV15" t="n">
         <v>-0</v>
       </c>
       <c r="FW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ15" t="n">
-        <v>0.04462418624405818</v>
+        <v>-0.0392241248176862</v>
       </c>
       <c r="GA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD15" t="n">
-        <v>-0.05108333755087999</v>
+        <v>0.06229019800014492</v>
       </c>
       <c r="GE15" t="n">
         <v>-0</v>
@@ -8960,7 +8960,7 @@
         <v>-0</v>
       </c>
       <c r="GG15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -10106,7 +10106,7 @@
         <v>0</v>
       </c>
       <c r="B18" t="n">
-        <v>0.1555227955103367</v>
+        <v>0.3740873085411197</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -10115,25 +10115,25 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.08280241633837762</v>
+        <v>-0.01212069175337799</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.07228254118439849</v>
+        <v>-0.1420221622722794</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1280013609926359</v>
+        <v>0.4550155857997566</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -10142,25 +10142,25 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.05768573777505789</v>
+        <v>-0.1030346101625517</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.07598714090533507</v>
+        <v>-0.1872297503630286</v>
       </c>
       <c r="P18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>0.01378244307605709</v>
+        <v>0.08850790259557874</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -10169,40 +10169,40 @@
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.004451178988662641</v>
+        <v>-0.08737791763617689</v>
       </c>
       <c r="X18" t="n">
-        <v>0.009296517155136153</v>
+        <v>-0.01195679459117023</v>
       </c>
       <c r="Y18" t="n">
         <v>-0</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>-0.004937052603166965</v>
+        <v>-0.03445648712941773</v>
       </c>
       <c r="AD18" t="n">
         <v>-0</v>
       </c>
       <c r="AE18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.01397086337945391</v>
+        <v>-0.2456376296061947</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.01246458326384953</v>
+        <v>0.01208147322881906</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI18" t="n">
         <v>-0</v>
@@ -10214,22 +10214,22 @@
         <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>0.01048426267962558</v>
+        <v>0.03864887039576933</v>
       </c>
       <c r="AM18" t="n">
         <v>-0</v>
       </c>
       <c r="AN18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
-        <v>-0.008843058167262783</v>
+        <v>-0.03478953138166604</v>
       </c>
       <c r="AP18" t="n">
-        <v>-0.01472490147678882</v>
+        <v>0.004348853773135694</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR18" t="n">
         <v>-0</v>
@@ -10238,28 +10238,28 @@
         <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.1072825700670186</v>
+        <v>0.4082565567656767</v>
       </c>
       <c r="AV18" t="n">
         <v>-0</v>
       </c>
       <c r="AW18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>-0.02880010261672456</v>
+        <v>-0.2569226983256364</v>
       </c>
       <c r="AY18" t="n">
-        <v>-0.02119212093019258</v>
+        <v>-0.1019174011449789</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
         <v>0</v>
@@ -10268,7 +10268,7 @@
         <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>0.03149636970574076</v>
+        <v>-0.007966828915457077</v>
       </c>
       <c r="BE18" t="n">
         <v>0</v>
@@ -10277,52 +10277,52 @@
         <v>0</v>
       </c>
       <c r="BG18" t="n">
-        <v>-0.05775229627875221</v>
+        <v>0.003299825105484479</v>
       </c>
       <c r="BH18" t="n">
-        <v>-0.05909104473704765</v>
+        <v>-0.06672767056896817</v>
       </c>
       <c r="BI18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK18" t="n">
         <v>0</v>
       </c>
       <c r="BL18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.03556435611813727</v>
+        <v>0.03790515352353375</v>
       </c>
       <c r="BN18" t="n">
         <v>-0</v>
       </c>
       <c r="BO18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP18" t="n">
-        <v>0.0160377211932141</v>
+        <v>0.05412149956945281</v>
       </c>
       <c r="BQ18" t="n">
-        <v>0.01704690532514525</v>
+        <v>-0.02904912448350688</v>
       </c>
       <c r="BR18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS18" t="n">
         <v>-0</v>
       </c>
       <c r="BT18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV18" t="n">
-        <v>0.05103091105067987</v>
+        <v>0.2284431608214726</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
@@ -10331,10 +10331,10 @@
         <v>0</v>
       </c>
       <c r="BY18" t="n">
-        <v>-0.01218046926464564</v>
+        <v>-0.06484531704446789</v>
       </c>
       <c r="BZ18" t="n">
-        <v>-0.01384008897907786</v>
+        <v>-0.108101791999787</v>
       </c>
       <c r="CA18" t="n">
         <v>-0</v>
@@ -10343,31 +10343,31 @@
         <v>-0</v>
       </c>
       <c r="CC18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE18" t="n">
-        <v>-0.02622308846222178</v>
+        <v>-0.106248834828522</v>
       </c>
       <c r="CF18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG18" t="n">
         <v>-0</v>
       </c>
       <c r="CH18" t="n">
-        <v>0.007127736093176795</v>
+        <v>0.02637823890535754</v>
       </c>
       <c r="CI18" t="n">
-        <v>0.01772200217820961</v>
+        <v>0.05235108424751526</v>
       </c>
       <c r="CJ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL18" t="n">
         <v>0</v>
@@ -10376,52 +10376,52 @@
         <v>0</v>
       </c>
       <c r="CN18" t="n">
-        <v>0.0008607606247808709</v>
+        <v>-0.1167963372686887</v>
       </c>
       <c r="CO18" t="n">
         <v>-0</v>
       </c>
       <c r="CP18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ18" t="n">
-        <v>-0.007075855757484145</v>
+        <v>0.1418910920064637</v>
       </c>
       <c r="CR18" t="n">
-        <v>-0.01179765717120735</v>
+        <v>0.06948314519810558</v>
       </c>
       <c r="CS18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV18" t="n">
         <v>-0</v>
       </c>
       <c r="CW18" t="n">
-        <v>-0.01997228527183853</v>
+        <v>-0.1042914444843911</v>
       </c>
       <c r="CX18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY18" t="n">
         <v>0</v>
       </c>
       <c r="CZ18" t="n">
-        <v>0.006098553888960175</v>
+        <v>0.01336787605902164</v>
       </c>
       <c r="DA18" t="n">
-        <v>0.01817422480022265</v>
+        <v>0.07393732256271993</v>
       </c>
       <c r="DB18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD18" t="n">
         <v>0</v>
@@ -10430,22 +10430,22 @@
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>-0.03236358042313904</v>
+        <v>-0.07613463879940778</v>
       </c>
       <c r="DG18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.05139714038333401</v>
+        <v>-0.2088158290936235</v>
       </c>
       <c r="DJ18" t="n">
-        <v>0.01369322867674388</v>
+        <v>0.0664830782668345</v>
       </c>
       <c r="DK18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL18" t="n">
         <v>-0</v>
@@ -10454,28 +10454,28 @@
         <v>0</v>
       </c>
       <c r="DN18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO18" t="n">
-        <v>-0.005787316285419271</v>
+        <v>-0.01453139399809695</v>
       </c>
       <c r="DP18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ18" t="n">
         <v>0</v>
       </c>
       <c r="DR18" t="n">
-        <v>0.01937102480609069</v>
+        <v>-0.04380413370108927</v>
       </c>
       <c r="DS18" t="n">
-        <v>-0.009748317299426336</v>
+        <v>0.04598420032442908</v>
       </c>
       <c r="DT18" t="n">
         <v>-0</v>
       </c>
       <c r="DU18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV18" t="n">
         <v>-0</v>
@@ -10484,49 +10484,49 @@
         <v>-0</v>
       </c>
       <c r="DX18" t="n">
-        <v>-0.02951577427682513</v>
+        <v>-0.008128724834928856</v>
       </c>
       <c r="DY18" t="n">
         <v>0</v>
       </c>
       <c r="DZ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA18" t="n">
-        <v>0.01498315768491325</v>
+        <v>-0.05739258479727879</v>
       </c>
       <c r="EB18" t="n">
-        <v>0.01825960522851271</v>
+        <v>0.02186635189298738</v>
       </c>
       <c r="EC18" t="n">
         <v>-0</v>
       </c>
       <c r="ED18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG18" t="n">
-        <v>-0.0315053328593496</v>
+        <v>-0.04910027289638845</v>
       </c>
       <c r="EH18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ18" t="n">
-        <v>0.00944317674849344</v>
+        <v>0.009966225733988959</v>
       </c>
       <c r="EK18" t="n">
-        <v>0.01334605781814872</v>
+        <v>-0.0008290111176221996</v>
       </c>
       <c r="EL18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM18" t="n">
         <v>-0</v>
@@ -10535,82 +10535,82 @@
         <v>-0</v>
       </c>
       <c r="EO18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP18" t="n">
-        <v>-0.01243019102766987</v>
+        <v>-0.03263751016830274</v>
       </c>
       <c r="EQ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER18" t="n">
         <v>-0</v>
       </c>
       <c r="ES18" t="n">
-        <v>0.002243096035829807</v>
+        <v>-0.01666909488296208</v>
       </c>
       <c r="ET18" t="n">
-        <v>-0.01165242559899074</v>
+        <v>0.1081606505080878</v>
       </c>
       <c r="EU18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV18" t="n">
         <v>0</v>
       </c>
       <c r="EW18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY18" t="n">
-        <v>-0.0208915055260241</v>
+        <v>-0.1236182570442468</v>
       </c>
       <c r="EZ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB18" t="n">
-        <v>0.009264301360075101</v>
+        <v>0.001119420975175839</v>
       </c>
       <c r="FC18" t="n">
-        <v>0.02170654796978215</v>
+        <v>0.04480882699908054</v>
       </c>
       <c r="FD18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE18" t="n">
         <v>-0</v>
       </c>
       <c r="FF18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG18" t="n">
         <v>0</v>
       </c>
       <c r="FH18" t="n">
-        <v>-0.01511337365004362</v>
+        <v>0.1682489665630392</v>
       </c>
       <c r="FI18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ18" t="n">
         <v>-0</v>
       </c>
       <c r="FK18" t="n">
-        <v>0.0113268961668335</v>
+        <v>-0.08182097191585727</v>
       </c>
       <c r="FL18" t="n">
-        <v>0.01985781488408164</v>
+        <v>0.1168730928665216</v>
       </c>
       <c r="FM18" t="n">
         <v>0</v>
       </c>
       <c r="FN18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO18" t="n">
         <v>0</v>
@@ -10619,63 +10619,63 @@
         <v>0</v>
       </c>
       <c r="FQ18" t="n">
-        <v>7.644719732458803e-05</v>
+        <v>0.001766033095943371</v>
       </c>
       <c r="FR18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS18" t="n">
         <v>-0</v>
       </c>
       <c r="FT18" t="n">
-        <v>-0.001509859052916248</v>
+        <v>-0.008890543018079875</v>
       </c>
       <c r="FU18" t="n">
-        <v>0.01880918805336776</v>
+        <v>-0.02826654740530361</v>
       </c>
       <c r="FV18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ18" t="n">
-        <v>0.001820653164314721</v>
+        <v>-0.03526500023485375</v>
       </c>
       <c r="GA18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB18" t="n">
         <v>-0</v>
       </c>
       <c r="GC18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD18" t="n">
-        <v>-0.005457780234660795</v>
+        <v>0.06675703004937075</v>
       </c>
       <c r="GE18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF18" t="n">
         <v>-0</v>
       </c>
       <c r="GG18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0.1266462604957166</v>
+        <v>0.2568294364946774</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -10684,10 +10684,10 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0359596502453245</v>
+        <v>0.08360029537802897</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1458807809284861</v>
+        <v>-0.1124021230301778</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>-0</v>
       </c>
       <c r="I19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1005695273084039</v>
+        <v>0.2217196001047798</v>
       </c>
       <c r="K19" t="n">
         <v>-0</v>
@@ -10708,43 +10708,43 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.002737779122467324</v>
+        <v>-0.007165351043765546</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0997243053547566</v>
+        <v>-0.1079803910484537</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>-0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.01760666690443216</v>
+        <v>-0.06928175277144705</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.03898100455986269</v>
+        <v>-0.04621480493013201</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.02367567826519899</v>
+        <v>-0.08056909819103956</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z19" t="n">
         <v>0</v>
@@ -10753,7 +10753,7 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.01516222809156062</v>
+        <v>0.0545615304003013</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -10762,43 +10762,43 @@
         <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>-0.02746700724001907</v>
+        <v>-0.03953367418522752</v>
       </c>
       <c r="AG19" t="n">
-        <v>-0.02875747820365326</v>
+        <v>0.05219803461472458</v>
       </c>
       <c r="AH19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK19" t="n">
-        <v>0.02170311454758471</v>
+        <v>0.01635961694893267</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
-        <v>-0.007094937415410008</v>
+        <v>0.0310684134670413</v>
       </c>
       <c r="AP19" t="n">
-        <v>-0.01299687962429524</v>
+        <v>0.01725490832228489</v>
       </c>
       <c r="AQ19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR19" t="n">
         <v>0</v>
@@ -10807,25 +10807,25 @@
         <v>0</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.08472652476482592</v>
+        <v>-0.0180578642833223</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AV19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW19" t="n">
         <v>0</v>
       </c>
       <c r="AX19" t="n">
-        <v>-0.1007914678233191</v>
+        <v>0.08887558904301493</v>
       </c>
       <c r="AY19" t="n">
-        <v>-0.08600565149370705</v>
+        <v>-0.007113253437926324</v>
       </c>
       <c r="AZ19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA19" t="n">
         <v>0</v>
@@ -10834,22 +10834,22 @@
         <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>0.01499549256361632</v>
+        <v>0.1617831854512066</v>
       </c>
       <c r="BD19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF19" t="n">
         <v>0</v>
       </c>
       <c r="BG19" t="n">
-        <v>0.01190784752073141</v>
+        <v>-0.02019540684000256</v>
       </c>
       <c r="BH19" t="n">
-        <v>-0.04702454220862393</v>
+        <v>0.002295561210419389</v>
       </c>
       <c r="BI19" t="n">
         <v>0</v>
@@ -10861,10 +10861,10 @@
         <v>-0</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.007487808577764449</v>
+        <v>-0.06679451029213296</v>
       </c>
       <c r="BM19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BN19" t="n">
         <v>-0</v>
@@ -10873,37 +10873,37 @@
         <v>0</v>
       </c>
       <c r="BP19" t="n">
-        <v>0.003610416424803363</v>
+        <v>-0.1113391538630767</v>
       </c>
       <c r="BQ19" t="n">
-        <v>0.008104688305153049</v>
+        <v>0.03653506681344443</v>
       </c>
       <c r="BR19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS19" t="n">
         <v>0</v>
       </c>
       <c r="BT19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU19" t="n">
-        <v>0.03643594286452657</v>
+        <v>-0.02642080760106553</v>
       </c>
       <c r="BV19" t="n">
         <v>0</v>
       </c>
       <c r="BW19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX19" t="n">
         <v>0</v>
       </c>
       <c r="BY19" t="n">
-        <v>-0.03598242985426318</v>
+        <v>-0.0702652693062062</v>
       </c>
       <c r="BZ19" t="n">
-        <v>-0.06421245250715174</v>
+        <v>-0.1104025499013803</v>
       </c>
       <c r="CA19" t="n">
         <v>-0</v>
@@ -10912,10 +10912,10 @@
         <v>0</v>
       </c>
       <c r="CC19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD19" t="n">
-        <v>-0.02249073403637856</v>
+        <v>-0.06422544393623388</v>
       </c>
       <c r="CE19" t="n">
         <v>0</v>
@@ -10927,13 +10927,13 @@
         <v>0</v>
       </c>
       <c r="CH19" t="n">
-        <v>0.01066464430794283</v>
+        <v>0.007021126430780321</v>
       </c>
       <c r="CI19" t="n">
-        <v>0.04343561869056956</v>
+        <v>0.03115380220022167</v>
       </c>
       <c r="CJ19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK19" t="n">
         <v>0</v>
@@ -10942,25 +10942,25 @@
         <v>-0</v>
       </c>
       <c r="CM19" t="n">
-        <v>0.004126862283695319</v>
+        <v>0.01181028276288585</v>
       </c>
       <c r="CN19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CO19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CQ19" t="n">
-        <v>0.06820944344543946</v>
+        <v>0.08373939567032432</v>
       </c>
       <c r="CR19" t="n">
-        <v>0.001346799260798693</v>
+        <v>-0.04380478783386278</v>
       </c>
       <c r="CS19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT19" t="n">
         <v>-0</v>
@@ -10969,7 +10969,7 @@
         <v>-0</v>
       </c>
       <c r="CV19" t="n">
-        <v>-0.02108001772460196</v>
+        <v>-0.06726026660128644</v>
       </c>
       <c r="CW19" t="n">
         <v>-0</v>
@@ -10981,40 +10981,40 @@
         <v>-0</v>
       </c>
       <c r="CZ19" t="n">
-        <v>0.01460815439289092</v>
+        <v>0.004563328884568592</v>
       </c>
       <c r="DA19" t="n">
-        <v>0.03937246904179714</v>
+        <v>0.03598994833441783</v>
       </c>
       <c r="DB19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC19" t="n">
         <v>-0</v>
       </c>
       <c r="DD19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE19" t="n">
-        <v>-0.0001534932277220459</v>
+        <v>-0.005146031250466448</v>
       </c>
       <c r="DF19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DG19" t="n">
         <v>-0</v>
       </c>
       <c r="DH19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI19" t="n">
-        <v>0.03079357996395915</v>
+        <v>-0.06032322361351384</v>
       </c>
       <c r="DJ19" t="n">
-        <v>0.001550474019576347</v>
+        <v>0.01431398112090277</v>
       </c>
       <c r="DK19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL19" t="n">
         <v>0</v>
@@ -11023,7 +11023,7 @@
         <v>0</v>
       </c>
       <c r="DN19" t="n">
-        <v>-0.0005372762060466832</v>
+        <v>-0.03987372890085466</v>
       </c>
       <c r="DO19" t="n">
         <v>0</v>
@@ -11032,13 +11032,13 @@
         <v>0</v>
       </c>
       <c r="DQ19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR19" t="n">
-        <v>0.03730876190525402</v>
+        <v>-0.05332094162376333</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.01723860783134225</v>
+        <v>0.08169112504517606</v>
       </c>
       <c r="DT19" t="n">
         <v>-0</v>
@@ -11047,37 +11047,37 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW19" t="n">
-        <v>-0.008746059748456648</v>
+        <v>0.02465871043844876</v>
       </c>
       <c r="DX19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DY19" t="n">
         <v>-0</v>
       </c>
       <c r="DZ19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA19" t="n">
-        <v>0.01650795672862657</v>
+        <v>0.1237911810008313</v>
       </c>
       <c r="EB19" t="n">
-        <v>0.03860945368572078</v>
+        <v>0.06352424167544639</v>
       </c>
       <c r="EC19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE19" t="n">
         <v>0</v>
       </c>
       <c r="EF19" t="n">
-        <v>-0.02203262574153988</v>
+        <v>0.003466002153019663</v>
       </c>
       <c r="EG19" t="n">
         <v>0</v>
@@ -11089,22 +11089,22 @@
         <v>0</v>
       </c>
       <c r="EJ19" t="n">
-        <v>-0.003408451035381646</v>
+        <v>-0.02625681375732344</v>
       </c>
       <c r="EK19" t="n">
-        <v>0.04728923408716374</v>
+        <v>0.0510532135942809</v>
       </c>
       <c r="EL19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN19" t="n">
         <v>0</v>
       </c>
       <c r="EO19" t="n">
-        <v>-0.01277627041603102</v>
+        <v>-0.03844273207820576</v>
       </c>
       <c r="EP19" t="n">
         <v>0</v>
@@ -11113,13 +11113,13 @@
         <v>-0</v>
       </c>
       <c r="ER19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES19" t="n">
-        <v>0.02803751493072065</v>
+        <v>0.006067814825159359</v>
       </c>
       <c r="ET19" t="n">
-        <v>0.002817743768328517</v>
+        <v>0.04406886628997701</v>
       </c>
       <c r="EU19" t="n">
         <v>0</v>
@@ -11131,7 +11131,7 @@
         <v>-0</v>
       </c>
       <c r="EX19" t="n">
-        <v>-0.01808398236400945</v>
+        <v>-0.05967497713790787</v>
       </c>
       <c r="EY19" t="n">
         <v>0</v>
@@ -11143,22 +11143,22 @@
         <v>0</v>
       </c>
       <c r="FB19" t="n">
-        <v>0.02408577528846209</v>
+        <v>-0.006747037493913817</v>
       </c>
       <c r="FC19" t="n">
-        <v>0.04115578127544132</v>
+        <v>0.04533085295682484</v>
       </c>
       <c r="FD19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE19" t="n">
         <v>0</v>
       </c>
       <c r="FF19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG19" t="n">
-        <v>0.007376195651755181</v>
+        <v>0.127769368547643</v>
       </c>
       <c r="FH19" t="n">
         <v>-0</v>
@@ -11167,13 +11167,13 @@
         <v>0</v>
       </c>
       <c r="FJ19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK19" t="n">
-        <v>0.01202097803954294</v>
+        <v>-5.861337664423544e-05</v>
       </c>
       <c r="FL19" t="n">
-        <v>-0.002121784118489793</v>
+        <v>0.1059281336776556</v>
       </c>
       <c r="FM19" t="n">
         <v>0</v>
@@ -11185,10 +11185,10 @@
         <v>-0</v>
       </c>
       <c r="FP19" t="n">
-        <v>0.0006546982649096399</v>
+        <v>0.003074093359563177</v>
       </c>
       <c r="FQ19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FR19" t="n">
         <v>-0</v>
@@ -11197,13 +11197,13 @@
         <v>0</v>
       </c>
       <c r="FT19" t="n">
-        <v>-0.0006216824476783274</v>
+        <v>0.001590208613466223</v>
       </c>
       <c r="FU19" t="n">
-        <v>0.01139849522618542</v>
+        <v>0.04096364891334509</v>
       </c>
       <c r="FV19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW19" t="n">
         <v>-0</v>
@@ -11212,28 +11212,28 @@
         <v>0</v>
       </c>
       <c r="FY19" t="n">
-        <v>0.00460258118434362</v>
+        <v>0.0725763631748053</v>
       </c>
       <c r="FZ19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GA19" t="n">
         <v>0</v>
       </c>
       <c r="GB19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD19" t="n">
-        <v>0.01054367872908787</v>
+        <v>0.07896609230274053</v>
       </c>
       <c r="GE19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG19" t="n">
         <v>0</v>
